--- a/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-medication-request.xlsx
+++ b/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-medication-request.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8983" uniqueCount="1022">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9007" uniqueCount="1028">
   <si>
     <t>Property</t>
   </si>
@@ -446,7 +446,7 @@
     <t>MedicationRequest.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
@@ -484,7 +484,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -518,7 +518,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -561,7 +561,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -1021,6 +1021,9 @@
     <t>period</t>
   </si>
   <si>
+    <t>Zeitraum der Einlösefrist</t>
+  </si>
+  <si>
     <t>MedicationRequest.extension:multiplePrescription.extension:period.id</t>
   </si>
   <si>
@@ -1347,6 +1350,9 @@
   <si>
     <t xml:space="preserve">Extension {https://gematik.de/fhir/epa-medication/StructureDefinition/indicator-bvg-extension}
 </t>
+  </si>
+  <si>
+    <t>Optional Extensions Element</t>
   </si>
   <si>
     <t>Indicator of whether this regulation is made in reference to the 'Bundesentschädigungsgesetz' or the 'Bundesversorgungsgesetz'.</t>
@@ -1463,6 +1469,9 @@
     <t>MedicationRequest.extension.value[x].type</t>
   </si>
   <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
     <t>MedicationRequest.extension:prescriberID.value[x].system</t>
   </si>
   <si>
@@ -1491,6 +1500,10 @@
   </si>
   <si>
     <t>MedicationRequest.extension.value[x].assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
   </si>
   <si>
     <t>MedicationRequest.extension:patientID</t>
@@ -2021,6 +2034,12 @@
 </t>
   </si>
   <si>
+    <t>An identifier intended for computation</t>
+  </si>
+  <si>
+    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
+  </si>
+  <si>
     <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="https://gematik.de/fhir/epa-medication/sid/rx-prescription-process-identifier"/&gt;
 &lt;/valueIdentifier&gt;</t>
@@ -2056,6 +2075,9 @@
     <t>completed</t>
   </si>
   <si>
+    <t>A coded concept specifying the state of the prescribing event. Describes the lifecycle of the prescription.</t>
+  </si>
+  <si>
     <t>https://gematik.de/fhir/terminology/ValueSet/ti-medication-request-status-vs</t>
   </si>
   <si>
@@ -2086,7 +2108,7 @@
     <t>Identifies the reasons for a given status.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason</t>
   </si>
   <si>
     <t>Request.statusReason</t>
@@ -2147,7 +2169,7 @@
     <t>A coded concept identifying the category of medication request.  For example, where the medication is to be consumed or administered, or the type of medication treatment.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-category</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Directions@@ -2203,7 +2225,7 @@
   </si>
   <si>
     <t>boolean
-Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)</t>
+Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Organization)</t>
   </si>
   <si>
     <t>Reported rather than primary record</t>
@@ -2326,7 +2348,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -2337,12 +2359,6 @@
   <si>
     <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-kvid-10}
 </t>
-  </si>
-  <si>
-    <t>Logical reference, when literal reference is not known</t>
-  </si>
-  <si>
-    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
   </si>
   <si>
     <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
@@ -2378,7 +2394,7 @@
     <t>MedicationRequest.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1)
+    <t xml:space="preserve">Reference(Encounter)
 </t>
   </si>
   <si>
@@ -2406,7 +2422,7 @@
     <t>MedicationRequest.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -2471,7 +2487,7 @@
     <t>MedicationRequest.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|Patient|4.0.1|Device|4.0.1|RelatedPerson|4.0.1|CareTeam|4.0.1)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Patient|Device|RelatedPerson|CareTeam)
 </t>
   </si>
   <si>
@@ -2505,7 +2521,7 @@
     <t>Identifies the type of individual that is desired to administer the medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/performer-role|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/performer-role</t>
   </si>
   <si>
     <t>Request.performerType</t>
@@ -2517,7 +2533,7 @@
     <t>MedicationRequest.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
 </t>
   </si>
   <si>
@@ -2548,7 +2564,7 @@
     <t>A coded concept indicating why the medication was ordered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -2569,7 +2585,7 @@
     <t>MedicationRequest.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1)
+    <t xml:space="preserve">Reference(Condition|Observation)
 </t>
   </si>
   <si>
@@ -2693,7 +2709,7 @@
     <t>Identifies the overall pattern of medication administratio.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy</t>
   </si>
   <si>
     <t>Act.code where classCode = LIST and moodCode = EVN</t>
@@ -2702,7 +2718,7 @@
     <t>MedicationRequest.insurance</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Coverage|4.0.1|ClaimResponse|4.0.1)
+    <t xml:space="preserve">Reference(Coverage|ClaimResponse)
 </t>
   </si>
   <si>
@@ -2752,7 +2768,7 @@
     <t>MedicationRequest.note.author[x]</t>
   </si>
   <si>
-    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
+    <t>Reference(Practitioner|Patient|RelatedPerson|Organization)
 string</t>
   </si>
   <si>
@@ -2821,6 +2837,123 @@
     <t>There are examples where a medication request may include the option of an oral dose or an Intravenous or Intramuscular dose.  For example, "Ondansetron 8mg orally or IV twice a day as needed for nausea" or "Compazine® (prochlorperazine) 5-10mg PO or 25mg PR bid prn nausea or vomiting".  In these cases, two medication requests would be created that could be grouped together.  The decision on which dose and route of administration to use is based on the patient's condition at the time the dose is needed.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+DosageStructuredOrFreeTextWarning:Die Dosierungsangabe darf entweder nur als Freitext oder nur als vollständige strukturierte Information erfolgen — eine Mischung ist nicht erlaubt. {(%resource.ofType(MedicationRequest).dosageInstruction | 
+ ofType(MedicationDispense).dosageInstruction | 
+ ofType(MedicationStatement).dosage).all(
+  (text.exists() and timing.empty() and doseAndRate.empty()) or
+  (text.empty() and (timing.exists() or doseAndRate.exists()))
+)
+}DosageStructuredRequiresBoth:Wenn eine strukturierte Dosierungsangabe erfolgt, müssen sowohl timing als auch doseAndRate angegeben werden. {(%resource.ofType(MedicationRequest).dosageInstruction | 
+ ofType(MedicationDispense).dosageInstruction | 
+ ofType(MedicationStatement).dosage).all(
+  (timing.exists() implies doseAndRate.exists()) and
+  (doseAndRate.exists() implies timing.exists())
+)
+}DosageDoseUnitSameCode:Die Dosiereinheit muss über alle Dosierungen gleich sein. {(%resource.ofType(MedicationRequest).dosageInstruction | ofType(MedicationDispense).dosageInstruction | ofType(MedicationStatement).dosage).all(
+doseAndRate.exists() implies
+  (
+    %resource.dosageInstruction.doseAndRate.dose.ofType(Quantity).code | 
+    %resource.dosageInstruction.doseAndRate.dose.ofType(Range).low.code | 
+    %resource.dosageInstruction.doseAndRate.dose.ofType(Range).high.code
+  ).distinct().count() = 1
+)}DosageWarnungViererschemaInText:Hinweis: In Dosage.text wurde ein Viererschema (z. B. 1-1-1-1) erkannt. Bitte prüfen, ob dies strukturiert abgebildet werden kann. {text.exists() implies text.matches('.*\\d+\\s*[-–]\\s*\\d+\\s*[-–]\\s*\\d+\\s*[-–]\\d+.*').not()}FreeTextSingleDosageOnlyWarning:Wenn eine Dosierung als reiner Freitext angegeben ist, soll nur genau ein Dosage-Element existieren. {(
+  (%resource.ofType(MedicationRequest).dosageInstruction |
+   %resource.ofType(MedicationDispense).dosageInstruction |
+   %resource.ofType(MedicationStatement).dosage
+  ).exists(text.exists() and timing.empty() and doseAndRate.empty())
+)
+implies
+(
+  (%resource.ofType(MedicationRequest).dosageInstruction |
+   %resource.ofType(MedicationDispense).dosageInstruction |
+   %resource.ofType(MedicationStatement).dosage
+  ).count() = 1
+)}DosageStructuredOrFreeText:Die Dosierungsangabe darf entweder nur als Freitext oder nur als vollständige strukturierte Information erfolgen — eine Mischung ist nicht erlaubt. {(%resource.ofType(MedicationRequest).dosageInstruction | 
+ ofType(MedicationDispense).dosageInstruction | 
+ ofType(MedicationStatement).dosage).all(
+  (text.exists() and timing.empty() and doseAndRate.empty()) or
+  (text.empty() and (timing.exists() or doseAndRate.exists()))
+)
+}DosageStructuredRequiresGeneratedText:Liegt eine strukturierte Dosierungsangabe vor (timing und doseAndRate belegt, text leer), muss die Extension GeneratedDosageInstructionsMeta vorhanden sein. {(
+  (%resource.ofType(MedicationRequest).dosageInstruction |
+   %resource.ofType(MedicationDispense).dosageInstruction |
+   %resource.ofType(MedicationStatement).dosage
+  ).exists(timing.exists() and doseAndRate.exists() and text.empty())
+)
+implies
+(
+%resource.extension.where(
+  url = 'http://ig.fhir.de/igs/medication/StructureDefinition/GeneratedDosageInstructionsMeta'
+).exists() and
+(
+  %resource.extension.where(
+    url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.renderedDosageInstruction'
+  ).exists() or
+  %resource.extension.where(
+    url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.renderedDosageInstruction'
+  ).exists() or
+  %resource.extension.where(
+    url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationStatement.renderedDosageInstruction'
+  ).exists()
+)
+)
+}FreeTextSingleDosageOnly:Wenn eine Dosierung als reiner Freitext angegeben ist, darf nur genau ein Dosage-Element existieren. {(
+  (%resource.ofType(MedicationRequest).dosageInstruction |
+   %resource.ofType(MedicationDispense).dosageInstruction |
+   %resource.ofType(MedicationStatement).dosage
+  ).exists(text.exists() and timing.empty() and doseAndRate.empty())
+)
+implies
+(
+  (%resource.ofType(MedicationRequest).dosageInstruction |
+   %resource.ofType(MedicationDispense).dosageInstruction |
+   %resource.ofType(MedicationStatement).dosage
+  ).count() = 1
+)}FreeTextMatchesRenderedText:Wenn eine Dosierung als reiner Freitext angegeben ist (text vorhanden, timing und doseAndRate leer) UND die Extension renderedDosageInstruction befüllt ist, muss der Wert in dosageInstruction.text mit dem Wert in der Extension übereinstimmen. {(
+  (%resource.ofType(MedicationRequest).dosageInstruction |
+   %resource.ofType(MedicationDispense).dosageInstruction |
+   %resource.ofType(MedicationStatement).dosage
+  ).where(text.exists() and timing.empty() and doseAndRate.empty()).exists()
+)
+implies
+(
+  (
+    %resource.ofType(MedicationRequest).exists() and
+    (
+      %resource.extension.where(
+        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.renderedDosageInstruction'
+      ).empty() or
+      %resource.extension.where(
+        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.renderedDosageInstruction'
+      ).value = %resource.dosageInstruction.text
+    )
+  ) or
+  (
+    %resource.ofType(MedicationDispense).exists() and
+    (
+      %resource.extension.where(
+        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.renderedDosageInstruction'
+      ).empty() or
+      %resource.extension.where(
+        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.renderedDosageInstruction'
+      ).value = %resource.dosageInstruction.text
+    )
+  ) or
+  (
+    %resource.ofType(MedicationStatement).exists() and
+    (
+      %resource.extension.where(
+        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationStatement.renderedDosageInstruction'
+      ).empty() or
+      %resource.extension.where(
+        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationStatement.renderedDosageInstruction'
+      ).value = %resource.dosage.text
+    )
+  )
+)}</t>
+  </si>
+  <si>
     <t>Request.occurrence[x]</t>
   </si>
   <si>
@@ -2896,7 +3029,7 @@
     <t>MedicationRequest.dispenseRequest.initialFill.quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+    <t xml:space="preserve">Quantity {SimpleQuantity}
 </t>
   </si>
   <si>
@@ -3141,7 +3274,7 @@
     <t>MedicationRequest.priorPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
+    <t xml:space="preserve">Reference(MedicationRequest)
 </t>
   </si>
   <si>
@@ -3164,7 +3297,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
+    <t xml:space="preserve">Reference(DetectedIssue)
 </t>
   </si>
   <si>
@@ -3183,7 +3316,7 @@
     <t>MedicationRequest.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance|4.0.1)
+    <t xml:space="preserve">Reference(Provenance)
 </t>
   </si>
   <si>
@@ -5561,7 +5694,7 @@
         <v>198</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -5588,7 +5721,9 @@
       <c r="M18" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="N18" s="2"/>
+      <c r="N18" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>81</v>
@@ -5646,7 +5781,7 @@
         <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>119</v>
@@ -5658,7 +5793,7 @@
         <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>81</v>
+        <v>192</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>81</v>
@@ -9208,7 +9343,7 @@
         <v>111</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>194</v>
+        <v>324</v>
       </c>
       <c r="M49" t="s" s="2">
         <v>195</v>
@@ -9294,7 +9429,7 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>210</v>
@@ -9409,7 +9544,7 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>212</v>
@@ -9524,7 +9659,7 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>214</v>
@@ -9641,7 +9776,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>220</v>
@@ -9667,7 +9802,7 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>232</v>
@@ -9736,7 +9871,7 @@
         <v>152</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>81</v>
@@ -9756,7 +9891,7 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>235</v>
@@ -9871,7 +10006,7 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>237</v>
@@ -9988,10 +10123,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -10014,16 +10149,16 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -10073,7 +10208,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -10082,7 +10217,7 @@
         <v>90</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>102</v>
@@ -10094,21 +10229,21 @@
         <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10131,23 +10266,23 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q57" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="R57" t="s" s="2">
         <v>81</v>
@@ -10192,7 +10327,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -10201,7 +10336,7 @@
         <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>102</v>
@@ -10213,24 +10348,24 @@
         <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>81</v>
@@ -10341,7 +10476,7 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>210</v>
@@ -10456,7 +10591,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>212</v>
@@ -10571,7 +10706,7 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>214</v>
@@ -10614,7 +10749,7 @@
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="S61" t="s" s="2">
         <v>81</v>
@@ -10688,7 +10823,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>220</v>
@@ -10714,7 +10849,7 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>232</v>
@@ -10803,7 +10938,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>235</v>
@@ -10918,7 +11053,7 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>237</v>
@@ -11035,10 +11170,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11064,16 +11199,16 @@
         <v>169</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -11101,10 +11236,10 @@
         <v>268</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>81</v>
@@ -11122,7 +11257,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -11143,7 +11278,7 @@
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
@@ -11154,10 +11289,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11180,19 +11315,19 @@
         <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>81</v>
@@ -11220,10 +11355,10 @@
         <v>148</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>81</v>
@@ -11241,7 +11376,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -11262,21 +11397,21 @@
         <v>81</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11302,29 +11437,29 @@
         <v>132</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="T67" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="U67" t="s" s="2">
         <v>81</v>
@@ -11360,7 +11495,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -11381,21 +11516,21 @@
         <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11421,13 +11556,13 @@
         <v>104</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -11441,7 +11576,7 @@
         <v>81</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>81</v>
@@ -11477,7 +11612,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -11498,21 +11633,21 @@
         <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11535,16 +11670,16 @@
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11594,7 +11729,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -11606,7 +11741,7 @@
         <v>152</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>81</v>
@@ -11615,21 +11750,21 @@
         <v>81</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11652,16 +11787,16 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -11711,7 +11846,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -11723,7 +11858,7 @@
         <v>152</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>81</v>
@@ -11732,21 +11867,21 @@
         <v>81</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11786,7 +11921,7 @@
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>81</v>
@@ -11860,10 +11995,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11886,7 +12021,7 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L72" t="s" s="2">
         <v>232</v>
@@ -11975,16 +12110,16 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -12003,15 +12138,17 @@
         <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>194</v>
+        <v>430</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>81</v>
@@ -12069,7 +12206,7 @@
         <v>80</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>119</v>
@@ -12081,7 +12218,7 @@
         <v>81</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
@@ -12092,7 +12229,7 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>203</v>
@@ -12207,14 +12344,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -12236,12 +12373,14 @@
         <v>111</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>81</v>
@@ -12311,7 +12450,7 @@
         <v>81</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>81</v>
@@ -12322,10 +12461,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12365,7 +12504,7 @@
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>81</v>
@@ -12439,10 +12578,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12468,10 +12607,10 @@
         <v>221</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -12554,16 +12693,16 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -12582,15 +12721,17 @@
         <v>81</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>194</v>
+        <v>430</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12648,7 +12789,7 @@
         <v>80</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>119</v>
@@ -12660,7 +12801,7 @@
         <v>81</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>81</v>
@@ -12671,7 +12812,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>203</v>
@@ -12786,14 +12927,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -12815,12 +12956,14 @@
         <v>111</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>81</v>
@@ -12890,7 +13033,7 @@
         <v>81</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>81</v>
@@ -12901,10 +13044,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12944,7 +13087,7 @@
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>81</v>
@@ -13018,10 +13161,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13047,10 +13190,10 @@
         <v>221</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -13133,16 +13276,16 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -13161,15 +13304,17 @@
         <v>81</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>194</v>
+        <v>430</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -13227,7 +13372,7 @@
         <v>80</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>119</v>
@@ -13239,7 +13384,7 @@
         <v>81</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>81</v>
@@ -13250,7 +13395,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>203</v>
@@ -13365,14 +13510,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -13394,12 +13539,14 @@
         <v>111</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>81</v>
@@ -13469,7 +13616,7 @@
         <v>81</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>81</v>
@@ -13480,10 +13627,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13523,7 +13670,7 @@
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>81</v>
@@ -13597,10 +13744,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13623,7 +13770,7 @@
         <v>81</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L87" t="s" s="2">
         <v>232</v>
@@ -13712,10 +13859,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13827,10 +13974,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13944,10 +14091,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13973,16 +14120,16 @@
         <v>169</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -14010,10 +14157,10 @@
         <v>268</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>81</v>
@@ -14031,7 +14178,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -14052,7 +14199,7 @@
         <v>81</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>81</v>
@@ -14063,10 +14210,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14089,19 +14236,19 @@
         <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -14129,10 +14276,10 @@
         <v>148</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>378</v>
+        <v>467</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -14150,7 +14297,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -14171,21 +14318,21 @@
         <v>81</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14211,16 +14358,16 @@
         <v>132</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14233,7 +14380,7 @@
         <v>81</v>
       </c>
       <c r="T92" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="U92" t="s" s="2">
         <v>81</v>
@@ -14269,7 +14416,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -14290,21 +14437,21 @@
         <v>81</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14330,13 +14477,13 @@
         <v>104</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -14350,7 +14497,7 @@
         <v>81</v>
       </c>
       <c r="T93" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="U93" t="s" s="2">
         <v>81</v>
@@ -14386,7 +14533,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -14407,21 +14554,21 @@
         <v>81</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14444,16 +14591,16 @@
         <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -14503,7 +14650,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -14515,7 +14662,7 @@
         <v>152</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>81</v>
@@ -14524,21 +14671,21 @@
         <v>81</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14561,16 +14708,16 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>412</v>
+        <v>478</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14620,7 +14767,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -14632,7 +14779,7 @@
         <v>152</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>81</v>
@@ -14641,27 +14788,27 @@
         <v>81</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -14680,15 +14827,17 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="L96" t="s" s="2">
         <v>194</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N96" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>81</v>
@@ -14746,7 +14895,7 @@
         <v>80</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>119</v>
@@ -14758,7 +14907,7 @@
         <v>81</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>81</v>
+        <v>192</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>81</v>
@@ -14769,7 +14918,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>203</v>
@@ -14884,7 +15033,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>205</v>
@@ -14999,10 +15148,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15042,7 +15191,7 @@
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>81</v>
@@ -15116,10 +15265,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15142,7 +15291,7 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L100" t="s" s="2">
         <v>232</v>
@@ -15231,10 +15380,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15346,10 +15495,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15463,10 +15612,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15492,16 +15641,16 @@
         <v>169</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>81</v>
@@ -15529,10 +15678,10 @@
         <v>268</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>81</v>
@@ -15550,7 +15699,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -15571,7 +15720,7 @@
         <v>81</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>81</v>
@@ -15582,10 +15731,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15608,19 +15757,19 @@
         <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>81</v>
@@ -15648,10 +15797,10 @@
         <v>148</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>81</v>
@@ -15669,7 +15818,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -15690,21 +15839,21 @@
         <v>81</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15730,16 +15879,16 @@
         <v>132</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>81</v>
@@ -15752,7 +15901,7 @@
         <v>81</v>
       </c>
       <c r="T105" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="U105" t="s" s="2">
         <v>81</v>
@@ -15788,7 +15937,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -15809,21 +15958,21 @@
         <v>81</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15849,13 +15998,13 @@
         <v>104</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15869,7 +16018,7 @@
         <v>81</v>
       </c>
       <c r="T106" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="U106" t="s" s="2">
         <v>81</v>
@@ -15905,7 +16054,7 @@
         <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -15926,21 +16075,21 @@
         <v>81</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15963,16 +16112,16 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -16022,7 +16171,7 @@
         <v>81</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -16034,7 +16183,7 @@
         <v>152</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>81</v>
@@ -16043,21 +16192,21 @@
         <v>81</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16080,16 +16229,16 @@
         <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -16139,7 +16288,7 @@
         <v>81</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -16151,7 +16300,7 @@
         <v>152</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>81</v>
@@ -16160,27 +16309,27 @@
         <v>81</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="D109" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -16199,15 +16348,17 @@
         <v>81</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N109" s="2"/>
+        <v>501</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>81</v>
@@ -16265,7 +16416,7 @@
         <v>80</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>119</v>
@@ -16277,7 +16428,7 @@
         <v>81</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>81</v>
+        <v>192</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>81</v>
@@ -16288,7 +16439,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>203</v>
@@ -16403,7 +16554,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>205</v>
@@ -16518,13 +16669,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>81</v>
@@ -16635,7 +16786,7 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>210</v>
@@ -16750,7 +16901,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>212</v>
@@ -16865,7 +17016,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>214</v>
@@ -16908,7 +17059,7 @@
       </c>
       <c r="Q115" s="2"/>
       <c r="R115" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="S115" t="s" s="2">
         <v>81</v>
@@ -16982,7 +17133,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>220</v>
@@ -17008,7 +17159,7 @@
         <v>81</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L116" t="s" s="2">
         <v>232</v>
@@ -17053,7 +17204,7 @@
         <v>81</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="AC116" s="2"/>
       <c r="AD116" t="s" s="2">
@@ -17095,13 +17246,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>220</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>81</v>
@@ -17132,7 +17283,7 @@
         <v>233</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -17143,7 +17294,7 @@
         <v>81</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>81</v>
@@ -17162,7 +17313,7 @@
       </c>
       <c r="Y117" s="2"/>
       <c r="Z117" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>81</v>
@@ -17212,7 +17363,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>235</v>
@@ -17327,7 +17478,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>237</v>
@@ -17444,10 +17595,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17473,16 +17624,16 @@
         <v>132</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>81</v>
@@ -17531,7 +17682,7 @@
         <v>81</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -17552,21 +17703,21 @@
         <v>81</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17592,13 +17743,13 @@
         <v>104</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -17648,7 +17799,7 @@
         <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -17669,21 +17820,21 @@
         <v>81</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17709,14 +17860,14 @@
         <v>169</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>81</v>
@@ -17765,7 +17916,7 @@
         <v>81</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -17786,21 +17937,21 @@
         <v>81</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17826,16 +17977,16 @@
         <v>104</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="N123" t="s" s="2">
         <v>278</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>81</v>
@@ -17884,7 +18035,7 @@
         <v>81</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -17905,21 +18056,21 @@
         <v>81</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17945,16 +18096,16 @@
         <v>221</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>81</v>
@@ -18003,7 +18154,7 @@
         <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -18024,24 +18175,24 @@
         <v>81</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D125" t="s" s="2">
         <v>81</v>
@@ -18152,7 +18303,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>210</v>
@@ -18267,7 +18418,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>212</v>
@@ -18382,7 +18533,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>214</v>
@@ -18425,7 +18576,7 @@
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>81</v>
@@ -18499,7 +18650,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>220</v>
@@ -18525,7 +18676,7 @@
         <v>81</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L129" t="s" s="2">
         <v>232</v>
@@ -18570,7 +18721,7 @@
         <v>81</v>
       </c>
       <c r="AB129" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="AC129" s="2"/>
       <c r="AD129" t="s" s="2">
@@ -18612,13 +18763,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>220</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>81</v>
@@ -18643,10 +18794,10 @@
         <v>104</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -18729,10 +18880,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18772,7 +18923,7 @@
       </c>
       <c r="Q131" s="2"/>
       <c r="R131" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="S131" t="s" s="2">
         <v>81</v>
@@ -18846,10 +18997,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18872,7 +19023,7 @@
         <v>81</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L132" t="s" s="2">
         <v>232</v>
@@ -18961,16 +19112,16 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="D133" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -18989,15 +19140,17 @@
         <v>81</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N133" s="2"/>
+        <v>575</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>81</v>
@@ -19055,7 +19208,7 @@
         <v>80</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>119</v>
@@ -19067,7 +19220,7 @@
         <v>81</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>81</v>
@@ -19078,7 +19231,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>203</v>
@@ -19193,18 +19346,18 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="G135" t="s" s="2">
         <v>80</v>
@@ -19222,12 +19375,14 @@
         <v>111</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N135" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>81</v>
@@ -19297,7 +19452,7 @@
         <v>81</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>81</v>
@@ -19308,16 +19463,16 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="D136" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
@@ -19339,12 +19494,14 @@
         <v>111</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N136" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
         <v>81</v>
@@ -19414,7 +19571,7 @@
         <v>81</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>81</v>
@@ -19425,7 +19582,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>210</v>
@@ -19540,14 +19697,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>212</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -19569,12 +19726,14 @@
         <v>111</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N138" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>81</v>
@@ -19644,7 +19803,7 @@
         <v>81</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>81</v>
@@ -19655,7 +19814,7 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>214</v>
@@ -19698,7 +19857,7 @@
       </c>
       <c r="Q139" s="2"/>
       <c r="R139" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="S139" t="s" s="2">
         <v>81</v>
@@ -19772,7 +19931,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>220</v>
@@ -19801,10 +19960,10 @@
         <v>221</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -19887,16 +20046,16 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="D141" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
@@ -19918,12 +20077,14 @@
         <v>111</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N141" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>81</v>
@@ -19993,7 +20154,7 @@
         <v>81</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>81</v>
@@ -20004,7 +20165,7 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>210</v>
@@ -20119,14 +20280,14 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>212</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
@@ -20148,12 +20309,14 @@
         <v>111</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N143" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>81</v>
@@ -20223,7 +20386,7 @@
         <v>81</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>81</v>
@@ -20234,7 +20397,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>214</v>
@@ -20277,7 +20440,7 @@
       </c>
       <c r="Q144" s="2"/>
       <c r="R144" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="S144" t="s" s="2">
         <v>81</v>
@@ -20351,7 +20514,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>220</v>
@@ -20380,10 +20543,10 @@
         <v>221</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -20466,16 +20629,16 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="D146" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
@@ -20497,12 +20660,14 @@
         <v>111</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N146" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N146" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>81</v>
@@ -20572,7 +20737,7 @@
         <v>81</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>81</v>
@@ -20583,7 +20748,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>210</v>
@@ -20698,14 +20863,14 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>212</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
@@ -20727,12 +20892,14 @@
         <v>111</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N148" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N148" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
         <v>81</v>
@@ -20802,7 +20969,7 @@
         <v>81</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>81</v>
@@ -20813,7 +20980,7 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>214</v>
@@ -20856,7 +21023,7 @@
       </c>
       <c r="Q149" s="2"/>
       <c r="R149" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="S149" t="s" s="2">
         <v>81</v>
@@ -20930,7 +21097,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>220</v>
@@ -20959,10 +21126,10 @@
         <v>221</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -21045,16 +21212,16 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="D151" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -21076,12 +21243,14 @@
         <v>111</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N151" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N151" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>81</v>
@@ -21151,7 +21320,7 @@
         <v>81</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>81</v>
@@ -21162,7 +21331,7 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>210</v>
@@ -21277,14 +21446,14 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>212</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
@@ -21306,12 +21475,14 @@
         <v>111</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N153" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>81</v>
@@ -21381,7 +21552,7 @@
         <v>81</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>81</v>
@@ -21392,7 +21563,7 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>214</v>
@@ -21435,7 +21606,7 @@
       </c>
       <c r="Q154" s="2"/>
       <c r="R154" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="S154" t="s" s="2">
         <v>81</v>
@@ -21509,7 +21680,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>220</v>
@@ -21538,10 +21709,10 @@
         <v>221</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -21624,16 +21795,16 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="D156" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -21655,12 +21826,14 @@
         <v>111</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N156" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N156" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
         <v>81</v>
@@ -21730,7 +21903,7 @@
         <v>81</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="AN156" t="s" s="2">
         <v>81</v>
@@ -21741,7 +21914,7 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>210</v>
@@ -21856,14 +22029,14 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>212</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
@@ -21885,12 +22058,14 @@
         <v>111</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N158" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N158" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
         <v>81</v>
@@ -21960,7 +22135,7 @@
         <v>81</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>81</v>
@@ -21971,7 +22146,7 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>214</v>
@@ -22014,7 +22189,7 @@
       </c>
       <c r="Q159" s="2"/>
       <c r="R159" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="S159" t="s" s="2">
         <v>81</v>
@@ -22088,7 +22263,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>220</v>
@@ -22117,10 +22292,10 @@
         <v>221</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -22203,10 +22378,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22246,7 +22421,7 @@
       </c>
       <c r="Q161" s="2"/>
       <c r="R161" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="S161" t="s" s="2">
         <v>81</v>
@@ -22320,10 +22495,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22346,7 +22521,7 @@
         <v>81</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L162" t="s" s="2">
         <v>232</v>
@@ -22435,16 +22610,16 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D163" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
@@ -22463,15 +22638,17 @@
         <v>81</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="N163" s="2"/>
+        <v>626</v>
+      </c>
+      <c r="N163" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
         <v>81</v>
@@ -22552,16 +22729,16 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D164" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
@@ -22580,15 +22757,17 @@
         <v>81</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="N164" s="2"/>
+        <v>631</v>
+      </c>
+      <c r="N164" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
         <v>81</v>
@@ -22646,7 +22825,7 @@
         <v>80</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>119</v>
@@ -22669,10 +22848,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22698,16 +22877,16 @@
         <v>111</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="N165" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>81</v>
@@ -22756,7 +22935,7 @@
         <v>117</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>79</v>
@@ -22788,10 +22967,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22814,16 +22993,16 @@
         <v>81</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -22861,10 +23040,10 @@
         <v>81</v>
       </c>
       <c r="AB166" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="AC166" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="AD166" t="s" s="2">
         <v>81</v>
@@ -22873,7 +23052,7 @@
         <v>117</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
@@ -22888,30 +23067,30 @@
         <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="D167" t="s" s="2">
         <v>81</v>
@@ -22933,16 +23112,16 @@
         <v>81</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>634</v>
+        <v>651</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>635</v>
+        <v>652</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -22953,7 +23132,7 @@
         <v>81</v>
       </c>
       <c r="S167" t="s" s="2">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="T167" t="s" s="2">
         <v>81</v>
@@ -22992,7 +23171,7 @@
         <v>81</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -23007,30 +23186,30 @@
         <v>102</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="D168" t="s" s="2">
         <v>81</v>
@@ -23052,16 +23231,16 @@
         <v>81</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>634</v>
+        <v>651</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>635</v>
+        <v>652</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
@@ -23072,7 +23251,7 @@
         <v>81</v>
       </c>
       <c r="S168" t="s" s="2">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="T168" t="s" s="2">
         <v>81</v>
@@ -23111,7 +23290,7 @@
         <v>81</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
@@ -23126,27 +23305,27 @@
         <v>102</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23172,13 +23351,13 @@
         <v>169</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -23186,7 +23365,7 @@
       </c>
       <c r="Q169" s="2"/>
       <c r="R169" t="s" s="2">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="S169" t="s" s="2">
         <v>81</v>
@@ -23206,9 +23385,11 @@
       <c r="X169" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="Y169" s="2"/>
+      <c r="Y169" t="s" s="2">
+        <v>663</v>
+      </c>
       <c r="Z169" t="s" s="2">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>81</v>
@@ -23226,7 +23407,7 @@
         <v>81</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>90</v>
@@ -23241,16 +23422,16 @@
         <v>102</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>81</v>
@@ -23258,10 +23439,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23284,16 +23465,16 @@
         <v>81</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -23322,10 +23503,10 @@
         <v>159</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>81</v>
@@ -23343,7 +23524,7 @@
         <v>81</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>79</v>
@@ -23358,27 +23539,27 @@
         <v>102</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="AL170" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="AN170" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO170" t="s" s="2">
-        <v>670</v>
+        <v>677</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23404,13 +23585,13 @@
         <v>169</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -23418,7 +23599,7 @@
       </c>
       <c r="Q171" s="2"/>
       <c r="R171" t="s" s="2">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="S171" t="s" s="2">
         <v>81</v>
@@ -23439,10 +23620,10 @@
         <v>268</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>81</v>
@@ -23460,7 +23641,7 @@
         <v>81</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>90</v>
@@ -23475,16 +23656,16 @@
         <v>102</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="AL171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>81</v>
@@ -23492,10 +23673,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23518,16 +23699,16 @@
         <v>81</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -23556,10 +23737,10 @@
         <v>159</v>
       </c>
       <c r="Y172" t="s" s="2">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="Z172" t="s" s="2">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="AA172" t="s" s="2">
         <v>81</v>
@@ -23577,7 +23758,7 @@
         <v>81</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>79</v>
@@ -23595,24 +23776,24 @@
         <v>81</v>
       </c>
       <c r="AL172" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="AM172" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="AN172" t="s" s="2">
         <v>687</v>
       </c>
-      <c r="AM172" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="AN172" t="s" s="2">
-        <v>680</v>
-      </c>
       <c r="AO172" t="s" s="2">
-        <v>670</v>
+        <v>677</v>
       </c>
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23638,10 +23819,10 @@
         <v>169</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -23671,10 +23852,10 @@
         <v>268</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>81</v>
@@ -23692,7 +23873,7 @@
         <v>81</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>79</v>
@@ -23707,16 +23888,16 @@
         <v>102</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="AL173" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="AO173" t="s" s="2">
         <v>81</v>
@@ -23724,10 +23905,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23753,13 +23934,13 @@
         <v>221</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -23809,7 +23990,7 @@
         <v>81</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>79</v>
@@ -23830,7 +24011,7 @@
         <v>81</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="AN174" t="s" s="2">
         <v>81</v>
@@ -23841,10 +24022,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23867,13 +24048,13 @@
         <v>91</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
@@ -23924,7 +24105,7 @@
         <v>81</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>79</v>
@@ -23945,7 +24126,7 @@
         <v>81</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="AN175" t="s" s="2">
         <v>81</v>
@@ -23956,10 +24137,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23982,16 +24163,16 @@
         <v>91</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -24041,7 +24222,7 @@
         <v>81</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>90</v>
@@ -24056,27 +24237,27 @@
         <v>102</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="AO176" t="s" s="2">
-        <v>716</v>
+        <v>723</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24099,16 +24280,16 @@
         <v>91</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -24158,7 +24339,7 @@
         <v>81</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>90</v>
@@ -24170,30 +24351,30 @@
         <v>152</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="AO177" t="s" s="2">
-        <v>726</v>
+        <v>733</v>
       </c>
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24305,10 +24486,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24422,10 +24603,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24451,13 +24632,13 @@
         <v>104</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
@@ -24507,7 +24688,7 @@
         <v>81</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>79</v>
@@ -24516,7 +24697,7 @@
         <v>90</v>
       </c>
       <c r="AI180" t="s" s="2">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="AJ180" t="s" s="2">
         <v>102</v>
@@ -24539,10 +24720,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24568,13 +24749,13 @@
         <v>132</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
@@ -24603,10 +24784,10 @@
         <v>148</v>
       </c>
       <c r="Y181" t="s" s="2">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="Z181" t="s" s="2">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>81</v>
@@ -24624,7 +24805,7 @@
         <v>81</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>79</v>
@@ -24656,10 +24837,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24682,16 +24863,16 @@
         <v>91</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>744</v>
+        <v>651</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>745</v>
+        <v>652</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
@@ -24741,7 +24922,7 @@
         <v>81</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>79</v>
@@ -24762,21 +24943,21 @@
         <v>81</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="AN182" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO182" t="s" s="2">
-        <v>749</v>
+        <v>754</v>
       </c>
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24802,13 +24983,13 @@
         <v>104</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
@@ -24858,7 +25039,7 @@
         <v>81</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
@@ -24890,10 +25071,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24916,16 +25097,16 @@
         <v>81</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
@@ -24975,7 +25156,7 @@
         <v>81</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>79</v>
@@ -24987,30 +25168,30 @@
         <v>152</v>
       </c>
       <c r="AJ184" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AK184" t="s" s="2">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="AM184" t="s" s="2">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>763</v>
+        <v>768</v>
       </c>
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25033,16 +25214,16 @@
         <v>81</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
@@ -25092,7 +25273,7 @@
         <v>81</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>79</v>
@@ -25104,19 +25285,19 @@
         <v>152</v>
       </c>
       <c r="AJ185" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AK185" t="s" s="2">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="AL185" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM185" t="s" s="2">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="AO185" t="s" s="2">
         <v>81</v>
@@ -25124,10 +25305,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25150,13 +25331,13 @@
         <v>91</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -25207,7 +25388,7 @@
         <v>81</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>79</v>
@@ -25222,27 +25403,27 @@
         <v>102</v>
       </c>
       <c r="AK186" t="s" s="2">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="AL186" t="s" s="2">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="AM186" t="s" s="2">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="AO186" t="s" s="2">
-        <v>778</v>
+        <v>783</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25265,16 +25446,16 @@
         <v>91</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
@@ -25324,7 +25505,7 @@
         <v>81</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -25336,19 +25517,19 @@
         <v>152</v>
       </c>
       <c r="AJ187" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AK187" t="s" s="2">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="AL187" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="AO187" t="s" s="2">
         <v>81</v>
@@ -25356,10 +25537,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25382,16 +25563,16 @@
         <v>81</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
@@ -25441,7 +25622,7 @@
         <v>81</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -25453,19 +25634,19 @@
         <v>152</v>
       </c>
       <c r="AJ188" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AK188" t="s" s="2">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="AL188" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>81</v>
@@ -25473,10 +25654,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25499,16 +25680,16 @@
         <v>91</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="O189" s="2"/>
       <c r="P189" t="s" s="2">
@@ -25537,28 +25718,28 @@
         <v>159</v>
       </c>
       <c r="Y189" t="s" s="2">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="Z189" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="AA189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE189" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF189" t="s" s="2">
         <v>797</v>
-      </c>
-      <c r="AA189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF189" t="s" s="2">
-        <v>792</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>79</v>
@@ -25573,27 +25754,27 @@
         <v>102</v>
       </c>
       <c r="AK189" t="s" s="2">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="AL189" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM189" t="s" s="2">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="AN189" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO189" t="s" s="2">
-        <v>670</v>
+        <v>677</v>
       </c>
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25616,16 +25797,16 @@
         <v>81</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="O190" s="2"/>
       <c r="P190" t="s" s="2">
@@ -25675,7 +25856,7 @@
         <v>81</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>79</v>
@@ -25687,7 +25868,7 @@
         <v>152</v>
       </c>
       <c r="AJ190" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AK190" t="s" s="2">
         <v>81</v>
@@ -25696,10 +25877,10 @@
         <v>81</v>
       </c>
       <c r="AM190" t="s" s="2">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="AN190" t="s" s="2">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="AO190" t="s" s="2">
         <v>81</v>
@@ -25707,10 +25888,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25733,16 +25914,16 @@
         <v>81</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
@@ -25771,28 +25952,28 @@
         <v>159</v>
       </c>
       <c r="Y191" t="s" s="2">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="Z191" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="AA191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE191" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF191" t="s" s="2">
         <v>811</v>
-      </c>
-      <c r="AA191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF191" t="s" s="2">
-        <v>806</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>79</v>
@@ -25807,27 +25988,27 @@
         <v>102</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="AO191" t="s" s="2">
-        <v>816</v>
+        <v>821</v>
       </c>
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25850,16 +26031,16 @@
         <v>81</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
@@ -25909,7 +26090,7 @@
         <v>81</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>79</v>
@@ -25921,19 +26102,19 @@
         <v>152</v>
       </c>
       <c r="AJ192" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AK192" t="s" s="2">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="AM192" t="s" s="2">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="AO192" t="s" s="2">
         <v>81</v>
@@ -25941,10 +26122,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25967,16 +26148,16 @@
         <v>91</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -26026,7 +26207,7 @@
         <v>81</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>79</v>
@@ -26041,13 +26222,13 @@
         <v>102</v>
       </c>
       <c r="AK193" t="s" s="2">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="AL193" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM193" t="s" s="2">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="AN193" t="s" s="2">
         <v>81</v>
@@ -26058,10 +26239,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26087,10 +26268,10 @@
         <v>132</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="N194" t="s" s="2">
         <v>287</v>
@@ -26143,7 +26324,7 @@
         <v>81</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>79</v>
@@ -26164,7 +26345,7 @@
         <v>81</v>
       </c>
       <c r="AM194" t="s" s="2">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="AN194" t="s" s="2">
         <v>81</v>
@@ -26175,10 +26356,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26201,16 +26382,16 @@
         <v>91</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
@@ -26260,7 +26441,7 @@
         <v>81</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>79</v>
@@ -26272,16 +26453,16 @@
         <v>152</v>
       </c>
       <c r="AJ195" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="AL195" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM195" t="s" s="2">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="AN195" t="s" s="2">
         <v>81</v>
@@ -26292,10 +26473,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26407,10 +26588,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26524,10 +26705,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26553,13 +26734,13 @@
         <v>104</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
@@ -26609,7 +26790,7 @@
         <v>81</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>79</v>
@@ -26618,7 +26799,7 @@
         <v>90</v>
       </c>
       <c r="AI198" t="s" s="2">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="AJ198" t="s" s="2">
         <v>102</v>
@@ -26641,10 +26822,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26670,13 +26851,13 @@
         <v>132</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="O199" s="2"/>
       <c r="P199" t="s" s="2">
@@ -26705,10 +26886,10 @@
         <v>148</v>
       </c>
       <c r="Y199" t="s" s="2">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="Z199" t="s" s="2">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="AA199" t="s" s="2">
         <v>81</v>
@@ -26726,7 +26907,7 @@
         <v>81</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>79</v>
@@ -26758,10 +26939,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26784,16 +26965,16 @@
         <v>91</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>744</v>
+        <v>651</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>745</v>
+        <v>652</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
@@ -26843,7 +27024,7 @@
         <v>81</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>79</v>
@@ -26864,21 +27045,21 @@
         <v>81</v>
       </c>
       <c r="AM200" t="s" s="2">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="AN200" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO200" t="s" s="2">
-        <v>749</v>
+        <v>754</v>
       </c>
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26904,13 +27085,13 @@
         <v>104</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
@@ -26960,7 +27141,7 @@
         <v>81</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>79</v>
@@ -26992,10 +27173,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -27018,17 +27199,17 @@
         <v>91</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" t="s" s="2">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>81</v>
@@ -27077,7 +27258,7 @@
         <v>81</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>79</v>
@@ -27092,27 +27273,27 @@
         <v>102</v>
       </c>
       <c r="AK202" t="s" s="2">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="AL202" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM202" t="s" s="2">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="AN202" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO202" t="s" s="2">
-        <v>749</v>
+        <v>754</v>
       </c>
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27135,16 +27316,16 @@
         <v>81</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="O203" s="2"/>
       <c r="P203" t="s" s="2">
@@ -27173,28 +27354,28 @@
         <v>159</v>
       </c>
       <c r="Y203" t="s" s="2">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="Z203" t="s" s="2">
+        <v>863</v>
+      </c>
+      <c r="AA203" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB203" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC203" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD203" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE203" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF203" t="s" s="2">
         <v>858</v>
-      </c>
-      <c r="AA203" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB203" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC203" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD203" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE203" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF203" t="s" s="2">
-        <v>853</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>79</v>
@@ -27215,21 +27396,21 @@
         <v>81</v>
       </c>
       <c r="AM203" t="s" s="2">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="AN203" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO203" t="s" s="2">
-        <v>670</v>
+        <v>677</v>
       </c>
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27252,16 +27433,16 @@
         <v>81</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="O204" s="2"/>
       <c r="P204" t="s" s="2">
@@ -27311,7 +27492,7 @@
         <v>81</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>79</v>
@@ -27323,16 +27504,16 @@
         <v>152</v>
       </c>
       <c r="AJ204" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AK204" t="s" s="2">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="AL204" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM204" t="s" s="2">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="AN204" t="s" s="2">
         <v>81</v>
@@ -27343,10 +27524,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27369,16 +27550,16 @@
         <v>81</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
@@ -27428,7 +27609,7 @@
         <v>81</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>79</v>
@@ -27443,13 +27624,13 @@
         <v>102</v>
       </c>
       <c r="AK205" t="s" s="2">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="AL205" t="s" s="2">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="AM205" t="s" s="2">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="AN205" t="s" s="2">
         <v>81</v>
@@ -27460,10 +27641,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27575,10 +27756,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27692,10 +27873,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>876</v>
+        <v>881</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>876</v>
+        <v>881</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27718,16 +27899,16 @@
         <v>91</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
@@ -27777,7 +27958,7 @@
         <v>81</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>79</v>
@@ -27798,7 +27979,7 @@
         <v>81</v>
       </c>
       <c r="AM208" t="s" s="2">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="AN208" t="s" s="2">
         <v>81</v>
@@ -27809,10 +27990,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27835,13 +28016,13 @@
         <v>91</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
@@ -27892,7 +28073,7 @@
         <v>81</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>79</v>
@@ -27913,7 +28094,7 @@
         <v>81</v>
       </c>
       <c r="AM209" t="s" s="2">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="AN209" t="s" s="2">
         <v>81</v>
@@ -27924,10 +28105,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -27950,16 +28131,16 @@
         <v>91</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
@@ -28009,7 +28190,7 @@
         <v>81</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>90</v>
@@ -28030,7 +28211,7 @@
         <v>81</v>
       </c>
       <c r="AM210" t="s" s="2">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="AN210" t="s" s="2">
         <v>81</v>
@@ -28041,10 +28222,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -28067,16 +28248,16 @@
         <v>81</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
@@ -28126,7 +28307,7 @@
         <v>81</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>79</v>
@@ -28135,19 +28316,19 @@
         <v>80</v>
       </c>
       <c r="AI211" t="s" s="2">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="AJ211" t="s" s="2">
-        <v>102</v>
+        <v>904</v>
       </c>
       <c r="AK211" t="s" s="2">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="AL211" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM211" t="s" s="2">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="AN211" t="s" s="2">
         <v>81</v>
@@ -28158,10 +28339,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28184,13 +28365,13 @@
         <v>81</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
@@ -28241,7 +28422,7 @@
         <v>81</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>79</v>
@@ -28259,10 +28440,10 @@
         <v>81</v>
       </c>
       <c r="AL212" t="s" s="2">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="AM212" t="s" s="2">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="AN212" t="s" s="2">
         <v>81</v>
@@ -28273,10 +28454,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28388,10 +28569,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28505,14 +28686,14 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="E215" s="2"/>
       <c r="F215" t="s" s="2">
@@ -28534,16 +28715,16 @@
         <v>111</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="N215" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O215" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>81</v>
@@ -28592,7 +28773,7 @@
         <v>81</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>79</v>
@@ -28624,10 +28805,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28650,16 +28831,16 @@
         <v>81</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>917</v>
+        <v>923</v>
       </c>
       <c r="O216" s="2"/>
       <c r="P216" t="s" s="2">
@@ -28709,7 +28890,7 @@
         <v>81</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>79</v>
@@ -28730,7 +28911,7 @@
         <v>81</v>
       </c>
       <c r="AM216" t="s" s="2">
-        <v>918</v>
+        <v>924</v>
       </c>
       <c r="AN216" t="s" s="2">
         <v>81</v>
@@ -28741,10 +28922,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>919</v>
+        <v>925</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28856,10 +29037,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -28973,14 +29154,14 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="E219" s="2"/>
       <c r="F219" t="s" s="2">
@@ -29002,16 +29183,16 @@
         <v>111</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="N219" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O219" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="P219" t="s" s="2">
         <v>81</v>
@@ -29060,7 +29241,7 @@
         <v>81</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>79</v>
@@ -29092,10 +29273,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29118,13 +29299,13 @@
         <v>81</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="N220" t="s" s="2">
         <v>243</v>
@@ -29177,7 +29358,7 @@
         <v>81</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>922</v>
+        <v>928</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>79</v>
@@ -29189,7 +29370,7 @@
         <v>152</v>
       </c>
       <c r="AJ220" t="s" s="2">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="AK220" t="s" s="2">
         <v>81</v>
@@ -29198,7 +29379,7 @@
         <v>81</v>
       </c>
       <c r="AM220" t="s" s="2">
-        <v>927</v>
+        <v>933</v>
       </c>
       <c r="AN220" t="s" s="2">
         <v>81</v>
@@ -29209,10 +29390,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -29235,13 +29416,13 @@
         <v>81</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="N221" t="s" s="2">
         <v>243</v>
@@ -29294,7 +29475,7 @@
         <v>81</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>79</v>
@@ -29306,7 +29487,7 @@
         <v>81</v>
       </c>
       <c r="AJ221" t="s" s="2">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="AK221" t="s" s="2">
         <v>81</v>
@@ -29315,7 +29496,7 @@
         <v>81</v>
       </c>
       <c r="AM221" t="s" s="2">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="AN221" t="s" s="2">
         <v>81</v>
@@ -29326,10 +29507,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -29352,13 +29533,13 @@
         <v>81</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="N222" t="s" s="2">
         <v>243</v>
@@ -29411,7 +29592,7 @@
         <v>81</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>79</v>
@@ -29423,7 +29604,7 @@
         <v>81</v>
       </c>
       <c r="AJ222" t="s" s="2">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="AK222" t="s" s="2">
         <v>81</v>
@@ -29432,7 +29613,7 @@
         <v>81</v>
       </c>
       <c r="AM222" t="s" s="2">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="AN222" t="s" s="2">
         <v>81</v>
@@ -29443,10 +29624,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29469,19 +29650,19 @@
         <v>81</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="N223" t="s" s="2">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="O223" t="s" s="2">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="P223" t="s" s="2">
         <v>81</v>
@@ -29530,7 +29711,7 @@
         <v>81</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>79</v>
@@ -29542,30 +29723,30 @@
         <v>152</v>
       </c>
       <c r="AJ223" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AK223" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL223" t="s" s="2">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="AM223" t="s" s="2">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="AN223" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO223" t="s" s="2">
-        <v>944</v>
+        <v>950</v>
       </c>
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29588,16 +29769,16 @@
         <v>81</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="O224" s="2"/>
       <c r="P224" t="s" s="2">
@@ -29647,7 +29828,7 @@
         <v>81</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>79</v>
@@ -29665,24 +29846,24 @@
         <v>81</v>
       </c>
       <c r="AL224" t="s" s="2">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="AM224" t="s" s="2">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="AN224" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO224" t="s" s="2">
-        <v>952</v>
+        <v>958</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -29705,13 +29886,13 @@
         <v>81</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="N225" t="s" s="2">
         <v>243</v>
@@ -29764,7 +29945,7 @@
         <v>81</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>79</v>
@@ -29776,30 +29957,30 @@
         <v>152</v>
       </c>
       <c r="AJ225" t="s" s="2">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="AK225" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL225" t="s" s="2">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="AM225" t="s" s="2">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="AN225" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO225" t="s" s="2">
-        <v>958</v>
+        <v>964</v>
       </c>
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -29911,10 +30092,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>960</v>
+        <v>966</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>960</v>
+        <v>966</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -30028,10 +30209,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -30057,10 +30238,10 @@
         <v>254</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="N228" t="s" s="2">
         <v>257</v>
@@ -30147,10 +30328,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -30179,7 +30360,7 @@
         <v>264</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>964</v>
+        <v>970</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" t="s" s="2">
@@ -30266,10 +30447,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>965</v>
+        <v>971</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>965</v>
+        <v>971</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -30383,10 +30564,10 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30429,7 +30610,7 @@
         <v>81</v>
       </c>
       <c r="S231" t="s" s="2">
-        <v>967</v>
+        <v>973</v>
       </c>
       <c r="T231" t="s" s="2">
         <v>81</v>
@@ -30500,10 +30681,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -30619,10 +30800,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -30645,16 +30826,16 @@
         <v>81</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>970</v>
+        <v>976</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="N233" t="s" s="2">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="O233" s="2"/>
       <c r="P233" t="s" s="2">
@@ -30704,7 +30885,7 @@
         <v>81</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>79</v>
@@ -30716,16 +30897,16 @@
         <v>81</v>
       </c>
       <c r="AJ233" t="s" s="2">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="AK233" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL233" t="s" s="2">
-        <v>973</v>
+        <v>979</v>
       </c>
       <c r="AM233" t="s" s="2">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="AN233" t="s" s="2">
         <v>81</v>
@@ -30736,10 +30917,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -30762,16 +30943,16 @@
         <v>81</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>412</v>
+        <v>478</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>976</v>
+        <v>982</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="N234" t="s" s="2">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="O234" s="2"/>
       <c r="P234" t="s" s="2">
@@ -30821,7 +31002,7 @@
         <v>81</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>79</v>
@@ -30833,7 +31014,7 @@
         <v>152</v>
       </c>
       <c r="AJ234" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AK234" t="s" s="2">
         <v>81</v>
@@ -30842,10 +31023,10 @@
         <v>81</v>
       </c>
       <c r="AM234" t="s" s="2">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="AN234" t="s" s="2">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="AO234" t="s" s="2">
         <v>81</v>
@@ -30853,10 +31034,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -30879,13 +31060,13 @@
         <v>81</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="N235" s="2"/>
       <c r="O235" s="2"/>
@@ -30936,7 +31117,7 @@
         <v>81</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>979</v>
+        <v>985</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>79</v>
@@ -30954,10 +31135,10 @@
         <v>81</v>
       </c>
       <c r="AL235" t="s" s="2">
-        <v>982</v>
+        <v>988</v>
       </c>
       <c r="AM235" t="s" s="2">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="AN235" t="s" s="2">
         <v>81</v>
@@ -30968,10 +31149,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>984</v>
+        <v>990</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>984</v>
+        <v>990</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -31083,10 +31264,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>985</v>
+        <v>991</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>985</v>
+        <v>991</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -31200,14 +31381,14 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="E238" s="2"/>
       <c r="F238" t="s" s="2">
@@ -31229,16 +31410,16 @@
         <v>111</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="N238" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O238" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="P238" t="s" s="2">
         <v>81</v>
@@ -31287,7 +31468,7 @@
         <v>81</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>79</v>
@@ -31319,10 +31500,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -31348,13 +31529,13 @@
         <v>221</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="N239" t="s" s="2">
-        <v>990</v>
+        <v>996</v>
       </c>
       <c r="O239" s="2"/>
       <c r="P239" t="s" s="2">
@@ -31404,7 +31585,7 @@
         <v>81</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>90</v>
@@ -31422,24 +31603,24 @@
         <v>81</v>
       </c>
       <c r="AL239" t="s" s="2">
-        <v>982</v>
+        <v>988</v>
       </c>
       <c r="AM239" t="s" s="2">
-        <v>991</v>
+        <v>997</v>
       </c>
       <c r="AN239" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO239" t="s" s="2">
-        <v>992</v>
+        <v>998</v>
       </c>
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -31462,16 +31643,16 @@
         <v>81</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>994</v>
+        <v>1000</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>995</v>
+        <v>1001</v>
       </c>
       <c r="N240" t="s" s="2">
-        <v>996</v>
+        <v>1002</v>
       </c>
       <c r="O240" s="2"/>
       <c r="P240" t="s" s="2">
@@ -31500,10 +31681,10 @@
         <v>159</v>
       </c>
       <c r="Y240" t="s" s="2">
-        <v>997</v>
+        <v>1003</v>
       </c>
       <c r="Z240" t="s" s="2">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="AA240" t="s" s="2">
         <v>81</v>
@@ -31521,7 +31702,7 @@
         <v>81</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>79</v>
@@ -31539,24 +31720,24 @@
         <v>81</v>
       </c>
       <c r="AL240" t="s" s="2">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="AM240" t="s" s="2">
-        <v>1000</v>
+        <v>1006</v>
       </c>
       <c r="AN240" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO240" t="s" s="2">
-        <v>1001</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -31579,16 +31760,16 @@
         <v>81</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>1003</v>
+        <v>1009</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="N241" t="s" s="2">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="O241" s="2"/>
       <c r="P241" t="s" s="2">
@@ -31638,7 +31819,7 @@
         <v>81</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>79</v>
@@ -31650,16 +31831,16 @@
         <v>152</v>
       </c>
       <c r="AJ241" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AK241" t="s" s="2">
-        <v>1006</v>
+        <v>1012</v>
       </c>
       <c r="AL241" t="s" s="2">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="AM241" t="s" s="2">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="AN241" t="s" s="2">
         <v>81</v>
@@ -31670,14 +31851,14 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>1008</v>
+        <v>1014</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>1008</v>
+        <v>1014</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
-        <v>1009</v>
+        <v>1015</v>
       </c>
       <c r="E242" s="2"/>
       <c r="F242" t="s" s="2">
@@ -31696,16 +31877,16 @@
         <v>81</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>1012</v>
+        <v>1018</v>
       </c>
       <c r="N242" t="s" s="2">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="O242" s="2"/>
       <c r="P242" t="s" s="2">
@@ -31755,7 +31936,7 @@
         <v>81</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>1008</v>
+        <v>1014</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>79</v>
@@ -31767,7 +31948,7 @@
         <v>152</v>
       </c>
       <c r="AJ242" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AK242" t="s" s="2">
         <v>81</v>
@@ -31776,7 +31957,7 @@
         <v>81</v>
       </c>
       <c r="AM242" t="s" s="2">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="AN242" t="s" s="2">
         <v>81</v>
@@ -31787,10 +31968,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -31813,16 +31994,16 @@
         <v>81</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>1016</v>
+        <v>1022</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>1018</v>
+        <v>1024</v>
       </c>
       <c r="N243" t="s" s="2">
-        <v>1019</v>
+        <v>1025</v>
       </c>
       <c r="O243" s="2"/>
       <c r="P243" t="s" s="2">
@@ -31872,7 +32053,7 @@
         <v>81</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>79</v>
@@ -31884,16 +32065,16 @@
         <v>152</v>
       </c>
       <c r="AJ243" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AK243" t="s" s="2">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="AL243" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM243" t="s" s="2">
-        <v>1021</v>
+        <v>1027</v>
       </c>
       <c r="AN243" t="s" s="2">
         <v>81</v>

--- a/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-medication-request.xlsx
+++ b/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-medication-request.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9007" uniqueCount="1028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8983" uniqueCount="1022">
   <si>
     <t>Property</t>
   </si>
@@ -446,7 +446,7 @@
     <t>MedicationRequest.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -484,7 +484,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -518,7 +518,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -561,7 +561,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -1021,9 +1021,6 @@
     <t>period</t>
   </si>
   <si>
-    <t>Zeitraum der Einlösefrist</t>
-  </si>
-  <si>
     <t>MedicationRequest.extension:multiplePrescription.extension:period.id</t>
   </si>
   <si>
@@ -1350,9 +1347,6 @@
   <si>
     <t xml:space="preserve">Extension {https://gematik.de/fhir/epa-medication/StructureDefinition/indicator-bvg-extension}
 </t>
-  </si>
-  <si>
-    <t>Optional Extensions Element</t>
   </si>
   <si>
     <t>Indicator of whether this regulation is made in reference to the 'Bundesentschädigungsgesetz' or the 'Bundesversorgungsgesetz'.</t>
@@ -1469,9 +1463,6 @@
     <t>MedicationRequest.extension.value[x].type</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
     <t>MedicationRequest.extension:prescriberID.value[x].system</t>
   </si>
   <si>
@@ -1500,10 +1491,6 @@
   </si>
   <si>
     <t>MedicationRequest.extension.value[x].assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
   </si>
   <si>
     <t>MedicationRequest.extension:patientID</t>
@@ -2034,12 +2021,6 @@
 </t>
   </si>
   <si>
-    <t>An identifier intended for computation</t>
-  </si>
-  <si>
-    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
-  </si>
-  <si>
     <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="https://gematik.de/fhir/epa-medication/sid/rx-prescription-process-identifier"/&gt;
 &lt;/valueIdentifier&gt;</t>
@@ -2075,9 +2056,6 @@
     <t>completed</t>
   </si>
   <si>
-    <t>A coded concept specifying the state of the prescribing event. Describes the lifecycle of the prescription.</t>
-  </si>
-  <si>
     <t>https://gematik.de/fhir/terminology/ValueSet/ti-medication-request-status-vs</t>
   </si>
   <si>
@@ -2108,7 +2086,7 @@
     <t>Identifies the reasons for a given status.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Request.statusReason</t>
@@ -2169,7 +2147,7 @@
     <t>A coded concept identifying the category of medication request.  For example, where the medication is to be consumed or administered, or the type of medication treatment.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-category|4.0.1</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Directions@@ -2225,7 +2203,7 @@
   </si>
   <si>
     <t>boolean
-Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Organization)</t>
+Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)</t>
   </si>
   <si>
     <t>Reported rather than primary record</t>
@@ -2348,7 +2326,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -2359,6 +2337,12 @@
   <si>
     <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-kvid-10}
 </t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
   </si>
   <si>
     <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
@@ -2394,7 +2378,7 @@
     <t>MedicationRequest.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -2422,7 +2406,7 @@
     <t>MedicationRequest.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -2487,7 +2471,7 @@
     <t>MedicationRequest.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Patient|Device|RelatedPerson|CareTeam)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|Patient|4.0.1|Device|4.0.1|RelatedPerson|4.0.1|CareTeam|4.0.1)
 </t>
   </si>
   <si>
@@ -2521,7 +2505,7 @@
     <t>Identifies the type of individual that is desired to administer the medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/performer-role</t>
+    <t>http://hl7.org/fhir/ValueSet/performer-role|4.0.1</t>
   </si>
   <si>
     <t>Request.performerType</t>
@@ -2533,7 +2517,7 @@
     <t>MedicationRequest.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -2564,7 +2548,7 @@
     <t>A coded concept indicating why the medication was ordered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -2585,7 +2569,7 @@
     <t>MedicationRequest.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1)
 </t>
   </si>
   <si>
@@ -2709,7 +2693,7 @@
     <t>Identifies the overall pattern of medication administratio.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy|4.0.1</t>
   </si>
   <si>
     <t>Act.code where classCode = LIST and moodCode = EVN</t>
@@ -2718,7 +2702,7 @@
     <t>MedicationRequest.insurance</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Coverage|ClaimResponse)
+    <t xml:space="preserve">Reference(Coverage|4.0.1|ClaimResponse|4.0.1)
 </t>
   </si>
   <si>
@@ -2768,7 +2752,7 @@
     <t>MedicationRequest.note.author[x]</t>
   </si>
   <si>
-    <t>Reference(Practitioner|Patient|RelatedPerson|Organization)
+    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 string</t>
   </si>
   <si>
@@ -2837,123 +2821,6 @@
     <t>There are examples where a medication request may include the option of an oral dose or an Intravenous or Intramuscular dose.  For example, "Ondansetron 8mg orally or IV twice a day as needed for nausea" or "Compazine® (prochlorperazine) 5-10mg PO or 25mg PR bid prn nausea or vomiting".  In these cases, two medication requests would be created that could be grouped together.  The decision on which dose and route of administration to use is based on the patient's condition at the time the dose is needed.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-DosageStructuredOrFreeTextWarning:Die Dosierungsangabe darf entweder nur als Freitext oder nur als vollständige strukturierte Information erfolgen — eine Mischung ist nicht erlaubt. {(%resource.ofType(MedicationRequest).dosageInstruction | 
- ofType(MedicationDispense).dosageInstruction | 
- ofType(MedicationStatement).dosage).all(
-  (text.exists() and timing.empty() and doseAndRate.empty()) or
-  (text.empty() and (timing.exists() or doseAndRate.exists()))
-)
-}DosageStructuredRequiresBoth:Wenn eine strukturierte Dosierungsangabe erfolgt, müssen sowohl timing als auch doseAndRate angegeben werden. {(%resource.ofType(MedicationRequest).dosageInstruction | 
- ofType(MedicationDispense).dosageInstruction | 
- ofType(MedicationStatement).dosage).all(
-  (timing.exists() implies doseAndRate.exists()) and
-  (doseAndRate.exists() implies timing.exists())
-)
-}DosageDoseUnitSameCode:Die Dosiereinheit muss über alle Dosierungen gleich sein. {(%resource.ofType(MedicationRequest).dosageInstruction | ofType(MedicationDispense).dosageInstruction | ofType(MedicationStatement).dosage).all(
-doseAndRate.exists() implies
-  (
-    %resource.dosageInstruction.doseAndRate.dose.ofType(Quantity).code | 
-    %resource.dosageInstruction.doseAndRate.dose.ofType(Range).low.code | 
-    %resource.dosageInstruction.doseAndRate.dose.ofType(Range).high.code
-  ).distinct().count() = 1
-)}DosageWarnungViererschemaInText:Hinweis: In Dosage.text wurde ein Viererschema (z. B. 1-1-1-1) erkannt. Bitte prüfen, ob dies strukturiert abgebildet werden kann. {text.exists() implies text.matches('.*\\d+\\s*[-–]\\s*\\d+\\s*[-–]\\s*\\d+\\s*[-–]\\d+.*').not()}FreeTextSingleDosageOnlyWarning:Wenn eine Dosierung als reiner Freitext angegeben ist, soll nur genau ein Dosage-Element existieren. {(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).exists(text.exists() and timing.empty() and doseAndRate.empty())
-)
-implies
-(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).count() = 1
-)}DosageStructuredOrFreeText:Die Dosierungsangabe darf entweder nur als Freitext oder nur als vollständige strukturierte Information erfolgen — eine Mischung ist nicht erlaubt. {(%resource.ofType(MedicationRequest).dosageInstruction | 
- ofType(MedicationDispense).dosageInstruction | 
- ofType(MedicationStatement).dosage).all(
-  (text.exists() and timing.empty() and doseAndRate.empty()) or
-  (text.empty() and (timing.exists() or doseAndRate.exists()))
-)
-}DosageStructuredRequiresGeneratedText:Liegt eine strukturierte Dosierungsangabe vor (timing und doseAndRate belegt, text leer), muss die Extension GeneratedDosageInstructionsMeta vorhanden sein. {(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).exists(timing.exists() and doseAndRate.exists() and text.empty())
-)
-implies
-(
-%resource.extension.where(
-  url = 'http://ig.fhir.de/igs/medication/StructureDefinition/GeneratedDosageInstructionsMeta'
-).exists() and
-(
-  %resource.extension.where(
-    url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.renderedDosageInstruction'
-  ).exists() or
-  %resource.extension.where(
-    url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.renderedDosageInstruction'
-  ).exists() or
-  %resource.extension.where(
-    url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationStatement.renderedDosageInstruction'
-  ).exists()
-)
-)
-}FreeTextSingleDosageOnly:Wenn eine Dosierung als reiner Freitext angegeben ist, darf nur genau ein Dosage-Element existieren. {(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).exists(text.exists() and timing.empty() and doseAndRate.empty())
-)
-implies
-(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).count() = 1
-)}FreeTextMatchesRenderedText:Wenn eine Dosierung als reiner Freitext angegeben ist (text vorhanden, timing und doseAndRate leer) UND die Extension renderedDosageInstruction befüllt ist, muss der Wert in dosageInstruction.text mit dem Wert in der Extension übereinstimmen. {(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).where(text.exists() and timing.empty() and doseAndRate.empty()).exists()
-)
-implies
-(
-  (
-    %resource.ofType(MedicationRequest).exists() and
-    (
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.renderedDosageInstruction'
-      ).empty() or
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.renderedDosageInstruction'
-      ).value = %resource.dosageInstruction.text
-    )
-  ) or
-  (
-    %resource.ofType(MedicationDispense).exists() and
-    (
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.renderedDosageInstruction'
-      ).empty() or
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.renderedDosageInstruction'
-      ).value = %resource.dosageInstruction.text
-    )
-  ) or
-  (
-    %resource.ofType(MedicationStatement).exists() and
-    (
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationStatement.renderedDosageInstruction'
-      ).empty() or
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationStatement.renderedDosageInstruction'
-      ).value = %resource.dosage.text
-    )
-  )
-)}</t>
-  </si>
-  <si>
     <t>Request.occurrence[x]</t>
   </si>
   <si>
@@ -3029,7 +2896,7 @@
     <t>MedicationRequest.dispenseRequest.initialFill.quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -3274,7 +3141,7 @@
     <t>MedicationRequest.priorPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -3297,7 +3164,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
+    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
 </t>
   </si>
   <si>
@@ -3316,7 +3183,7 @@
     <t>MedicationRequest.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -5694,7 +5561,7 @@
         <v>198</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -5721,9 +5588,7 @@
       <c r="M18" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="N18" t="s" s="2">
-        <v>114</v>
-      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>81</v>
@@ -5781,7 +5646,7 @@
         <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>119</v>
@@ -5793,7 +5658,7 @@
         <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>192</v>
+        <v>81</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>81</v>
@@ -9343,7 +9208,7 @@
         <v>111</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>324</v>
+        <v>194</v>
       </c>
       <c r="M49" t="s" s="2">
         <v>195</v>
@@ -9429,7 +9294,7 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>210</v>
@@ -9544,7 +9409,7 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>212</v>
@@ -9659,7 +9524,7 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>214</v>
@@ -9776,7 +9641,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>220</v>
@@ -9802,7 +9667,7 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>232</v>
@@ -9871,7 +9736,7 @@
         <v>152</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>81</v>
@@ -9891,7 +9756,7 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>235</v>
@@ -10006,7 +9871,7 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>237</v>
@@ -10123,10 +9988,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B56" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -10149,16 +10014,16 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -10208,16 +10073,16 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI56" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>102</v>
@@ -10229,21 +10094,21 @@
         <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO56" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>342</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B57" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10266,69 +10131,69 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q57" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="R57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="R57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>349</v>
-      </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
@@ -10336,7 +10201,7 @@
         <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>102</v>
@@ -10348,24 +10213,24 @@
         <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>351</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>81</v>
@@ -10476,7 +10341,7 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>210</v>
@@ -10591,7 +10456,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>212</v>
@@ -10706,7 +10571,7 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>214</v>
@@ -10749,7 +10614,7 @@
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="S61" t="s" s="2">
         <v>81</v>
@@ -10823,7 +10688,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>220</v>
@@ -10849,7 +10714,7 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>232</v>
@@ -10938,7 +10803,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>235</v>
@@ -11053,7 +10918,7 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>237</v>
@@ -11170,10 +11035,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="B65" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11199,16 +11064,16 @@
         <v>169</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -11236,28 +11101,28 @@
         <v>268</v>
       </c>
       <c r="Y65" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="Z65" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="Z65" t="s" s="2">
+      <c r="AA65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -11278,7 +11143,7 @@
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
@@ -11289,10 +11154,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11315,19 +11180,19 @@
         <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="N66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>81</v>
@@ -11355,28 +11220,28 @@
         <v>148</v>
       </c>
       <c r="Y66" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="Z66" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="Z66" t="s" s="2">
+      <c r="AA66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -11397,21 +11262,21 @@
         <v>81</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11437,65 +11302,65 @@
         <v>132</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T67" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="S67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T67" t="s" s="2">
+      <c r="U67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -11516,21 +11381,21 @@
         <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO67" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>392</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11556,13 +11421,13 @@
         <v>104</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -11576,43 +11441,43 @@
         <v>81</v>
       </c>
       <c r="T68" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -11633,21 +11498,21 @@
         <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>401</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11670,16 +11535,16 @@
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11729,7 +11594,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -11741,30 +11606,30 @@
         <v>152</v>
       </c>
       <c r="AJ69" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AK69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AN69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO69" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>410</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11787,16 +11652,16 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -11846,7 +11711,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -11858,30 +11723,30 @@
         <v>152</v>
       </c>
       <c r="AJ70" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AK70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AN70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO70" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>420</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11921,7 +11786,7 @@
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>81</v>
@@ -11995,10 +11860,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12021,7 +11886,7 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L72" t="s" s="2">
         <v>232</v>
@@ -12110,16 +11975,16 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -12138,17 +12003,15 @@
         <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="L73" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>114</v>
-      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>81</v>
@@ -12206,7 +12069,7 @@
         <v>80</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>119</v>
@@ -12218,7 +12081,7 @@
         <v>81</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>81</v>
@@ -12229,7 +12092,7 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>203</v>
@@ -12344,14 +12207,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -12373,14 +12236,12 @@
         <v>111</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>81</v>
@@ -12450,7 +12311,7 @@
         <v>81</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>81</v>
@@ -12461,10 +12322,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12504,7 +12365,7 @@
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>81</v>
@@ -12578,10 +12439,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12607,10 +12468,10 @@
         <v>221</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -12693,16 +12554,16 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -12721,17 +12582,15 @@
         <v>81</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>430</v>
+        <v>194</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12789,7 +12648,7 @@
         <v>80</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>119</v>
@@ -12801,7 +12660,7 @@
         <v>81</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>81</v>
@@ -12812,7 +12671,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>203</v>
@@ -12927,14 +12786,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -12956,14 +12815,12 @@
         <v>111</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>81</v>
@@ -13033,7 +12890,7 @@
         <v>81</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>81</v>
@@ -13044,10 +12901,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13087,7 +12944,7 @@
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>81</v>
@@ -13161,10 +13018,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13190,10 +13047,10 @@
         <v>221</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -13276,16 +13133,16 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -13304,17 +13161,15 @@
         <v>81</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>430</v>
+        <v>194</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -13372,7 +13227,7 @@
         <v>80</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>119</v>
@@ -13384,7 +13239,7 @@
         <v>81</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>81</v>
@@ -13395,7 +13250,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>203</v>
@@ -13510,14 +13365,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -13539,14 +13394,12 @@
         <v>111</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>81</v>
@@ -13616,7 +13469,7 @@
         <v>81</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>81</v>
@@ -13627,10 +13480,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13670,7 +13523,7 @@
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>81</v>
@@ -13744,10 +13597,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13770,7 +13623,7 @@
         <v>81</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="L87" t="s" s="2">
         <v>232</v>
@@ -13859,10 +13712,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13974,10 +13827,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14091,10 +13944,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14120,16 +13973,16 @@
         <v>169</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="N90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -14157,28 +14010,28 @@
         <v>268</v>
       </c>
       <c r="Y90" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="Z90" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="Z90" t="s" s="2">
+      <c r="AA90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF90" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -14199,7 +14052,7 @@
         <v>81</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>81</v>
@@ -14210,10 +14063,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14236,19 +14089,19 @@
         <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L91" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="L91" t="s" s="2">
+      <c r="M91" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="N91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -14276,11 +14129,11 @@
         <v>148</v>
       </c>
       <c r="Y91" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="Z91" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="Z91" t="s" s="2">
-        <v>467</v>
-      </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
       </c>
@@ -14297,7 +14150,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -14318,21 +14171,21 @@
         <v>81</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14358,16 +14211,16 @@
         <v>132</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="M92" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N92" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14380,43 +14233,43 @@
         <v>81</v>
       </c>
       <c r="T92" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -14437,21 +14290,21 @@
         <v>81</v>
       </c>
       <c r="AM92" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO92" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>392</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14477,13 +14330,13 @@
         <v>104</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -14497,43 +14350,43 @@
         <v>81</v>
       </c>
       <c r="T93" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF93" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -14554,21 +14407,21 @@
         <v>81</v>
       </c>
       <c r="AM93" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO93" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>401</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14591,16 +14444,16 @@
         <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -14650,7 +14503,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -14662,30 +14515,30 @@
         <v>152</v>
       </c>
       <c r="AJ94" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM94" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AK94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM94" t="s" s="2">
+      <c r="AN94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO94" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>410</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14708,16 +14561,16 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>478</v>
+        <v>412</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14767,7 +14620,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -14779,36 +14632,36 @@
         <v>152</v>
       </c>
       <c r="AJ95" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM95" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AK95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM95" t="s" s="2">
+      <c r="AN95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO95" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>420</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -14827,17 +14680,15 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="L96" t="s" s="2">
         <v>194</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>81</v>
@@ -14895,7 +14746,7 @@
         <v>80</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>119</v>
@@ -14907,7 +14758,7 @@
         <v>81</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>192</v>
+        <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>81</v>
@@ -14918,7 +14769,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>203</v>
@@ -15033,7 +14884,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>205</v>
@@ -15148,10 +14999,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15191,7 +15042,7 @@
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>81</v>
@@ -15265,10 +15116,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15291,7 +15142,7 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="L100" t="s" s="2">
         <v>232</v>
@@ -15380,10 +15231,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15495,10 +15346,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15612,10 +15463,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15641,16 +15492,16 @@
         <v>169</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>81</v>
@@ -15678,28 +15529,28 @@
         <v>268</v>
       </c>
       <c r="Y103" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="Z103" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="Z103" t="s" s="2">
+      <c r="AA103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF103" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -15720,7 +15571,7 @@
         <v>81</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>81</v>
@@ -15731,10 +15582,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15757,19 +15608,19 @@
         <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L104" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="L104" t="s" s="2">
+      <c r="M104" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="N104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>81</v>
@@ -15797,28 +15648,28 @@
         <v>148</v>
       </c>
       <c r="Y104" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="Z104" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="Z104" t="s" s="2">
+      <c r="AA104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF104" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -15839,21 +15690,21 @@
         <v>81</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15879,16 +15730,16 @@
         <v>132</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="M105" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N105" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="N105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>81</v>
@@ -15901,43 +15752,43 @@
         <v>81</v>
       </c>
       <c r="T105" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF105" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -15958,21 +15809,21 @@
         <v>81</v>
       </c>
       <c r="AM105" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO105" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>392</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15998,13 +15849,13 @@
         <v>104</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -16018,43 +15869,43 @@
         <v>81</v>
       </c>
       <c r="T106" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF106" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -16075,21 +15926,21 @@
         <v>81</v>
       </c>
       <c r="AM106" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO106" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>401</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16112,16 +15963,16 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -16171,7 +16022,7 @@
         <v>81</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -16183,30 +16034,30 @@
         <v>152</v>
       </c>
       <c r="AJ107" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM107" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AK107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM107" t="s" s="2">
+      <c r="AN107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO107" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>410</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16229,16 +16080,16 @@
         <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L108" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="L108" t="s" s="2">
+      <c r="M108" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="N108" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -16288,7 +16139,7 @@
         <v>81</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -16300,36 +16151,36 @@
         <v>152</v>
       </c>
       <c r="AJ108" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM108" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AK108" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM108" t="s" s="2">
+      <c r="AN108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO108" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>420</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="D109" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -16348,17 +16199,15 @@
         <v>81</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>81</v>
@@ -16416,7 +16265,7 @@
         <v>80</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>119</v>
@@ -16428,7 +16277,7 @@
         <v>81</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>192</v>
+        <v>81</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>81</v>
@@ -16439,7 +16288,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>203</v>
@@ -16554,7 +16403,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>205</v>
@@ -16669,13 +16518,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>81</v>
@@ -16786,7 +16635,7 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>210</v>
@@ -16901,7 +16750,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>212</v>
@@ -17016,7 +16865,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>214</v>
@@ -17059,7 +16908,7 @@
       </c>
       <c r="Q115" s="2"/>
       <c r="R115" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="S115" t="s" s="2">
         <v>81</v>
@@ -17133,7 +16982,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>220</v>
@@ -17159,7 +17008,7 @@
         <v>81</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L116" t="s" s="2">
         <v>232</v>
@@ -17204,7 +17053,7 @@
         <v>81</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="AC116" s="2"/>
       <c r="AD116" t="s" s="2">
@@ -17246,13 +17095,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>220</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>81</v>
@@ -17283,7 +17132,7 @@
         <v>233</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -17294,7 +17143,7 @@
         <v>81</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>81</v>
@@ -17313,7 +17162,7 @@
       </c>
       <c r="Y117" s="2"/>
       <c r="Z117" t="s" s="2">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>81</v>
@@ -17363,7 +17212,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>235</v>
@@ -17478,7 +17327,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>237</v>
@@ -17595,10 +17444,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17624,16 +17473,16 @@
         <v>132</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>81</v>
@@ -17682,7 +17531,7 @@
         <v>81</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -17703,21 +17552,21 @@
         <v>81</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>525</v>
+        <v>521</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17743,13 +17592,13 @@
         <v>104</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -17799,7 +17648,7 @@
         <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -17820,21 +17669,21 @@
         <v>81</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>533</v>
+        <v>529</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17860,14 +17709,14 @@
         <v>169</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>81</v>
@@ -17916,7 +17765,7 @@
         <v>81</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -17937,21 +17786,21 @@
         <v>81</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>540</v>
+        <v>536</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17977,16 +17826,16 @@
         <v>104</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="N123" t="s" s="2">
         <v>278</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>81</v>
@@ -18035,7 +17884,7 @@
         <v>81</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -18056,21 +17905,21 @@
         <v>81</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>548</v>
+        <v>544</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18096,16 +17945,16 @@
         <v>221</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>81</v>
@@ -18154,7 +18003,7 @@
         <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -18175,24 +18024,24 @@
         <v>81</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>557</v>
+        <v>553</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="D125" t="s" s="2">
         <v>81</v>
@@ -18303,7 +18152,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>210</v>
@@ -18418,7 +18267,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>212</v>
@@ -18533,7 +18382,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>214</v>
@@ -18576,7 +18425,7 @@
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>81</v>
@@ -18650,7 +18499,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>220</v>
@@ -18676,7 +18525,7 @@
         <v>81</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L129" t="s" s="2">
         <v>232</v>
@@ -18721,7 +18570,7 @@
         <v>81</v>
       </c>
       <c r="AB129" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="AC129" s="2"/>
       <c r="AD129" t="s" s="2">
@@ -18763,13 +18612,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>220</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>81</v>
@@ -18794,10 +18643,10 @@
         <v>104</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -18880,10 +18729,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18923,7 +18772,7 @@
       </c>
       <c r="Q131" s="2"/>
       <c r="R131" t="s" s="2">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="S131" t="s" s="2">
         <v>81</v>
@@ -18997,10 +18846,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19023,7 +18872,7 @@
         <v>81</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L132" t="s" s="2">
         <v>232</v>
@@ -19112,16 +18961,16 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="D133" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -19140,17 +18989,15 @@
         <v>81</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="N133" s="2"/>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>81</v>
@@ -19208,7 +19055,7 @@
         <v>80</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>119</v>
@@ -19220,7 +19067,7 @@
         <v>81</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>81</v>
@@ -19231,7 +19078,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>203</v>
@@ -19346,18 +19193,18 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G135" t="s" s="2">
         <v>80</v>
@@ -19375,14 +19222,12 @@
         <v>111</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N135" s="2"/>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>81</v>
@@ -19452,7 +19297,7 @@
         <v>81</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>81</v>
@@ -19463,16 +19308,16 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="D136" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
@@ -19494,14 +19339,12 @@
         <v>111</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N136" s="2"/>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
         <v>81</v>
@@ -19571,7 +19414,7 @@
         <v>81</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>81</v>
@@ -19582,7 +19425,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>210</v>
@@ -19697,14 +19540,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>212</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -19726,14 +19569,12 @@
         <v>111</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N138" s="2"/>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>81</v>
@@ -19803,7 +19644,7 @@
         <v>81</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>81</v>
@@ -19814,7 +19655,7 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>214</v>
@@ -19857,7 +19698,7 @@
       </c>
       <c r="Q139" s="2"/>
       <c r="R139" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="S139" t="s" s="2">
         <v>81</v>
@@ -19931,7 +19772,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>220</v>
@@ -19960,10 +19801,10 @@
         <v>221</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -20046,16 +19887,16 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="D141" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
@@ -20077,14 +19918,12 @@
         <v>111</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N141" s="2"/>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>81</v>
@@ -20154,7 +19993,7 @@
         <v>81</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>81</v>
@@ -20165,7 +20004,7 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>210</v>
@@ -20280,14 +20119,14 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>212</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
@@ -20309,14 +20148,12 @@
         <v>111</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N143" s="2"/>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>81</v>
@@ -20386,7 +20223,7 @@
         <v>81</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>81</v>
@@ -20397,7 +20234,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>214</v>
@@ -20440,7 +20277,7 @@
       </c>
       <c r="Q144" s="2"/>
       <c r="R144" t="s" s="2">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="S144" t="s" s="2">
         <v>81</v>
@@ -20514,7 +20351,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>220</v>
@@ -20543,10 +20380,10 @@
         <v>221</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -20629,16 +20466,16 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D146" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
@@ -20660,14 +20497,12 @@
         <v>111</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N146" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N146" s="2"/>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>81</v>
@@ -20737,7 +20572,7 @@
         <v>81</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>81</v>
@@ -20748,7 +20583,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>210</v>
@@ -20863,14 +20698,14 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>212</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
@@ -20892,14 +20727,12 @@
         <v>111</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N148" s="2"/>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
         <v>81</v>
@@ -20969,7 +20802,7 @@
         <v>81</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>81</v>
@@ -20980,7 +20813,7 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>214</v>
@@ -21023,7 +20856,7 @@
       </c>
       <c r="Q149" s="2"/>
       <c r="R149" t="s" s="2">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="S149" t="s" s="2">
         <v>81</v>
@@ -21097,7 +20930,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>220</v>
@@ -21126,10 +20959,10 @@
         <v>221</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -21212,16 +21045,16 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="D151" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -21243,14 +21076,12 @@
         <v>111</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N151" s="2"/>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>81</v>
@@ -21320,7 +21151,7 @@
         <v>81</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>81</v>
@@ -21331,7 +21162,7 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>210</v>
@@ -21446,14 +21277,14 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>212</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
@@ -21475,14 +21306,12 @@
         <v>111</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N153" s="2"/>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>81</v>
@@ -21552,7 +21381,7 @@
         <v>81</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>81</v>
@@ -21563,7 +21392,7 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>214</v>
@@ -21606,7 +21435,7 @@
       </c>
       <c r="Q154" s="2"/>
       <c r="R154" t="s" s="2">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="S154" t="s" s="2">
         <v>81</v>
@@ -21680,7 +21509,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>220</v>
@@ -21709,10 +21538,10 @@
         <v>221</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -21795,16 +21624,16 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>205</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="D156" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -21826,14 +21655,12 @@
         <v>111</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N156" s="2"/>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
         <v>81</v>
@@ -21903,7 +21730,7 @@
         <v>81</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN156" t="s" s="2">
         <v>81</v>
@@ -21914,7 +21741,7 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>210</v>
@@ -22029,14 +21856,14 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>212</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
@@ -22058,14 +21885,12 @@
         <v>111</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N158" s="2"/>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
         <v>81</v>
@@ -22135,7 +21960,7 @@
         <v>81</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>81</v>
@@ -22146,7 +21971,7 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>214</v>
@@ -22189,7 +22014,7 @@
       </c>
       <c r="Q159" s="2"/>
       <c r="R159" t="s" s="2">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="S159" t="s" s="2">
         <v>81</v>
@@ -22263,7 +22088,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>220</v>
@@ -22292,10 +22117,10 @@
         <v>221</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -22378,10 +22203,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22421,7 +22246,7 @@
       </c>
       <c r="Q161" s="2"/>
       <c r="R161" t="s" s="2">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="S161" t="s" s="2">
         <v>81</v>
@@ -22495,10 +22320,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22521,7 +22346,7 @@
         <v>81</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L162" t="s" s="2">
         <v>232</v>
@@ -22610,16 +22435,16 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="D163" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
@@ -22638,17 +22463,15 @@
         <v>81</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="N163" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>622</v>
+      </c>
+      <c r="N163" s="2"/>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
         <v>81</v>
@@ -22729,16 +22552,16 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="D164" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
@@ -22757,17 +22580,15 @@
         <v>81</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="N164" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>627</v>
+      </c>
+      <c r="N164" s="2"/>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
         <v>81</v>
@@ -22825,7 +22646,7 @@
         <v>80</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>119</v>
@@ -22848,10 +22669,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22877,16 +22698,16 @@
         <v>111</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="N165" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>81</v>
@@ -22935,7 +22756,7 @@
         <v>117</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>79</v>
@@ -22967,10 +22788,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22993,16 +22814,16 @@
         <v>81</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -23040,10 +22861,10 @@
         <v>81</v>
       </c>
       <c r="AB166" t="s" s="2">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="AC166" t="s" s="2">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="AD166" t="s" s="2">
         <v>81</v>
@@ -23052,7 +22873,7 @@
         <v>117</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
@@ -23067,30 +22888,30 @@
         <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AL166" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AM166" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AN166" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AO166" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="AL166" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AM166" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="AN166" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="AO166" t="s" s="2">
-        <v>647</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="D167" t="s" s="2">
         <v>81</v>
@@ -23112,16 +22933,16 @@
         <v>81</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>651</v>
+        <v>634</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -23132,7 +22953,7 @@
         <v>81</v>
       </c>
       <c r="S167" t="s" s="2">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="T167" t="s" s="2">
         <v>81</v>
@@ -23171,7 +22992,7 @@
         <v>81</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -23186,30 +23007,30 @@
         <v>102</v>
       </c>
       <c r="AK167" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AL167" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AM167" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AN167" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AO167" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="AL167" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AM167" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="AN167" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="AO167" t="s" s="2">
-        <v>647</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="D168" t="s" s="2">
         <v>81</v>
@@ -23231,16 +23052,16 @@
         <v>81</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>651</v>
+        <v>634</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
@@ -23251,7 +23072,7 @@
         <v>81</v>
       </c>
       <c r="S168" t="s" s="2">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="T168" t="s" s="2">
         <v>81</v>
@@ -23290,7 +23111,7 @@
         <v>81</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
@@ -23305,27 +23126,27 @@
         <v>102</v>
       </c>
       <c r="AK168" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AL168" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AM168" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AN168" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AO168" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="AL168" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AM168" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="AN168" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="AO168" t="s" s="2">
-        <v>647</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23351,13 +23172,13 @@
         <v>169</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -23365,7 +23186,7 @@
       </c>
       <c r="Q169" s="2"/>
       <c r="R169" t="s" s="2">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="S169" t="s" s="2">
         <v>81</v>
@@ -23385,11 +23206,9 @@
       <c r="X169" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="Y169" t="s" s="2">
-        <v>663</v>
-      </c>
+      <c r="Y169" s="2"/>
       <c r="Z169" t="s" s="2">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>81</v>
@@ -23407,7 +23226,7 @@
         <v>81</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>90</v>
@@ -23422,16 +23241,16 @@
         <v>102</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>81</v>
@@ -23439,10 +23258,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23465,16 +23284,16 @@
         <v>81</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -23503,10 +23322,10 @@
         <v>159</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>81</v>
@@ -23524,7 +23343,7 @@
         <v>81</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>79</v>
@@ -23539,27 +23358,27 @@
         <v>102</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="AL170" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="AN170" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO170" t="s" s="2">
-        <v>677</v>
+        <v>670</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23585,13 +23404,13 @@
         <v>169</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -23599,7 +23418,7 @@
       </c>
       <c r="Q171" s="2"/>
       <c r="R171" t="s" s="2">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="S171" t="s" s="2">
         <v>81</v>
@@ -23620,10 +23439,10 @@
         <v>268</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>81</v>
@@ -23641,7 +23460,7 @@
         <v>81</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>90</v>
@@ -23656,16 +23475,16 @@
         <v>102</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="AL171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>81</v>
@@ -23673,10 +23492,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23699,16 +23518,16 @@
         <v>81</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -23737,10 +23556,10 @@
         <v>159</v>
       </c>
       <c r="Y172" t="s" s="2">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="Z172" t="s" s="2">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="AA172" t="s" s="2">
         <v>81</v>
@@ -23758,7 +23577,7 @@
         <v>81</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>79</v>
@@ -23776,24 +23595,24 @@
         <v>81</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="AO172" t="s" s="2">
-        <v>677</v>
+        <v>670</v>
       </c>
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23819,10 +23638,10 @@
         <v>169</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -23852,10 +23671,10 @@
         <v>268</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>81</v>
@@ -23873,7 +23692,7 @@
         <v>81</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>79</v>
@@ -23888,16 +23707,16 @@
         <v>102</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="AL173" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="AO173" t="s" s="2">
         <v>81</v>
@@ -23905,10 +23724,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23934,13 +23753,13 @@
         <v>221</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -23990,7 +23809,7 @@
         <v>81</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>79</v>
@@ -24011,7 +23830,7 @@
         <v>81</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="AN174" t="s" s="2">
         <v>81</v>
@@ -24022,10 +23841,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -24048,13 +23867,13 @@
         <v>91</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
@@ -24105,7 +23924,7 @@
         <v>81</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>79</v>
@@ -24126,7 +23945,7 @@
         <v>81</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="AN175" t="s" s="2">
         <v>81</v>
@@ -24137,10 +23956,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -24163,16 +23982,16 @@
         <v>91</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -24222,7 +24041,7 @@
         <v>81</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>90</v>
@@ -24237,27 +24056,27 @@
         <v>102</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="AO176" t="s" s="2">
-        <v>723</v>
+        <v>716</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24280,16 +24099,16 @@
         <v>91</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -24339,7 +24158,7 @@
         <v>81</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>90</v>
@@ -24351,30 +24170,30 @@
         <v>152</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="AO177" t="s" s="2">
-        <v>733</v>
+        <v>726</v>
       </c>
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24486,10 +24305,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24603,10 +24422,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24632,13 +24451,13 @@
         <v>104</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
@@ -24688,7 +24507,7 @@
         <v>81</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>79</v>
@@ -24697,7 +24516,7 @@
         <v>90</v>
       </c>
       <c r="AI180" t="s" s="2">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="AJ180" t="s" s="2">
         <v>102</v>
@@ -24720,10 +24539,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24749,13 +24568,13 @@
         <v>132</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
@@ -24784,10 +24603,10 @@
         <v>148</v>
       </c>
       <c r="Y181" t="s" s="2">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="Z181" t="s" s="2">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>81</v>
@@ -24805,7 +24624,7 @@
         <v>81</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>79</v>
@@ -24837,10 +24656,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24863,16 +24682,16 @@
         <v>91</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>651</v>
+        <v>744</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>652</v>
+        <v>745</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
@@ -24922,7 +24741,7 @@
         <v>81</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>79</v>
@@ -24943,21 +24762,21 @@
         <v>81</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="AN182" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO182" t="s" s="2">
-        <v>754</v>
+        <v>749</v>
       </c>
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24983,13 +24802,13 @@
         <v>104</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
@@ -25039,7 +24858,7 @@
         <v>81</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
@@ -25071,10 +24890,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25097,16 +24916,16 @@
         <v>81</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
@@ -25156,7 +24975,7 @@
         <v>81</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>79</v>
@@ -25168,30 +24987,30 @@
         <v>152</v>
       </c>
       <c r="AJ184" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AK184" t="s" s="2">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="AM184" t="s" s="2">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>768</v>
+        <v>763</v>
       </c>
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25214,16 +25033,16 @@
         <v>81</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
@@ -25273,7 +25092,7 @@
         <v>81</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>79</v>
@@ -25285,19 +25104,19 @@
         <v>152</v>
       </c>
       <c r="AJ185" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AK185" t="s" s="2">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="AL185" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM185" t="s" s="2">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="AO185" t="s" s="2">
         <v>81</v>
@@ -25305,10 +25124,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25331,13 +25150,13 @@
         <v>91</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -25388,7 +25207,7 @@
         <v>81</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>79</v>
@@ -25403,27 +25222,27 @@
         <v>102</v>
       </c>
       <c r="AK186" t="s" s="2">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="AL186" t="s" s="2">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="AM186" t="s" s="2">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="AO186" t="s" s="2">
-        <v>783</v>
+        <v>778</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25446,16 +25265,16 @@
         <v>91</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
@@ -25505,7 +25324,7 @@
         <v>81</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -25517,19 +25336,19 @@
         <v>152</v>
       </c>
       <c r="AJ187" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AK187" t="s" s="2">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="AL187" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="AO187" t="s" s="2">
         <v>81</v>
@@ -25537,10 +25356,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25563,16 +25382,16 @@
         <v>81</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
@@ -25622,7 +25441,7 @@
         <v>81</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -25634,19 +25453,19 @@
         <v>152</v>
       </c>
       <c r="AJ188" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AK188" t="s" s="2">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="AL188" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>81</v>
@@ -25654,10 +25473,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25680,16 +25499,16 @@
         <v>91</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="O189" s="2"/>
       <c r="P189" t="s" s="2">
@@ -25718,10 +25537,10 @@
         <v>159</v>
       </c>
       <c r="Y189" t="s" s="2">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="Z189" t="s" s="2">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="AA189" t="s" s="2">
         <v>81</v>
@@ -25739,7 +25558,7 @@
         <v>81</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>79</v>
@@ -25754,27 +25573,27 @@
         <v>102</v>
       </c>
       <c r="AK189" t="s" s="2">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="AL189" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM189" t="s" s="2">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="AN189" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO189" t="s" s="2">
-        <v>677</v>
+        <v>670</v>
       </c>
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25797,16 +25616,16 @@
         <v>81</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="O190" s="2"/>
       <c r="P190" t="s" s="2">
@@ -25856,7 +25675,7 @@
         <v>81</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>79</v>
@@ -25868,7 +25687,7 @@
         <v>152</v>
       </c>
       <c r="AJ190" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AK190" t="s" s="2">
         <v>81</v>
@@ -25877,10 +25696,10 @@
         <v>81</v>
       </c>
       <c r="AM190" t="s" s="2">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="AN190" t="s" s="2">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="AO190" t="s" s="2">
         <v>81</v>
@@ -25888,10 +25707,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25914,16 +25733,16 @@
         <v>81</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
@@ -25952,10 +25771,10 @@
         <v>159</v>
       </c>
       <c r="Y191" t="s" s="2">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="Z191" t="s" s="2">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>81</v>
@@ -25973,7 +25792,7 @@
         <v>81</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>79</v>
@@ -25988,27 +25807,27 @@
         <v>102</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="AO191" t="s" s="2">
-        <v>821</v>
+        <v>816</v>
       </c>
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -26031,16 +25850,16 @@
         <v>81</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
@@ -26090,7 +25909,7 @@
         <v>81</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>79</v>
@@ -26102,19 +25921,19 @@
         <v>152</v>
       </c>
       <c r="AJ192" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AK192" t="s" s="2">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="AM192" t="s" s="2">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="AO192" t="s" s="2">
         <v>81</v>
@@ -26122,10 +25941,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -26148,16 +25967,16 @@
         <v>91</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -26207,7 +26026,7 @@
         <v>81</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>79</v>
@@ -26222,13 +26041,13 @@
         <v>102</v>
       </c>
       <c r="AK193" t="s" s="2">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="AL193" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM193" t="s" s="2">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="AN193" t="s" s="2">
         <v>81</v>
@@ -26239,10 +26058,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26268,10 +26087,10 @@
         <v>132</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="N194" t="s" s="2">
         <v>287</v>
@@ -26324,7 +26143,7 @@
         <v>81</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>79</v>
@@ -26345,7 +26164,7 @@
         <v>81</v>
       </c>
       <c r="AM194" t="s" s="2">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="AN194" t="s" s="2">
         <v>81</v>
@@ -26356,10 +26175,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26382,16 +26201,16 @@
         <v>91</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
@@ -26441,7 +26260,7 @@
         <v>81</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>79</v>
@@ -26453,16 +26272,16 @@
         <v>152</v>
       </c>
       <c r="AJ195" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="AL195" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM195" t="s" s="2">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="AN195" t="s" s="2">
         <v>81</v>
@@ -26473,10 +26292,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26588,10 +26407,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26705,10 +26524,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26734,13 +26553,13 @@
         <v>104</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
@@ -26790,7 +26609,7 @@
         <v>81</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>79</v>
@@ -26799,7 +26618,7 @@
         <v>90</v>
       </c>
       <c r="AI198" t="s" s="2">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="AJ198" t="s" s="2">
         <v>102</v>
@@ -26822,10 +26641,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26851,13 +26670,13 @@
         <v>132</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="O199" s="2"/>
       <c r="P199" t="s" s="2">
@@ -26886,10 +26705,10 @@
         <v>148</v>
       </c>
       <c r="Y199" t="s" s="2">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="Z199" t="s" s="2">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="AA199" t="s" s="2">
         <v>81</v>
@@ -26907,7 +26726,7 @@
         <v>81</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>79</v>
@@ -26939,10 +26758,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26965,16 +26784,16 @@
         <v>91</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>651</v>
+        <v>744</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>652</v>
+        <v>745</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
@@ -27024,7 +26843,7 @@
         <v>81</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>79</v>
@@ -27045,21 +26864,21 @@
         <v>81</v>
       </c>
       <c r="AM200" t="s" s="2">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="AN200" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO200" t="s" s="2">
-        <v>754</v>
+        <v>749</v>
       </c>
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -27085,13 +26904,13 @@
         <v>104</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
@@ -27141,7 +26960,7 @@
         <v>81</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>79</v>
@@ -27173,10 +26992,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -27199,17 +27018,17 @@
         <v>91</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" t="s" s="2">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>81</v>
@@ -27258,7 +27077,7 @@
         <v>81</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>79</v>
@@ -27273,27 +27092,27 @@
         <v>102</v>
       </c>
       <c r="AK202" t="s" s="2">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="AL202" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM202" t="s" s="2">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="AN202" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO202" t="s" s="2">
-        <v>754</v>
+        <v>749</v>
       </c>
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27316,16 +27135,16 @@
         <v>81</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="O203" s="2"/>
       <c r="P203" t="s" s="2">
@@ -27354,10 +27173,10 @@
         <v>159</v>
       </c>
       <c r="Y203" t="s" s="2">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="Z203" t="s" s="2">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="AA203" t="s" s="2">
         <v>81</v>
@@ -27375,7 +27194,7 @@
         <v>81</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>79</v>
@@ -27396,21 +27215,21 @@
         <v>81</v>
       </c>
       <c r="AM203" t="s" s="2">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="AN203" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO203" t="s" s="2">
-        <v>677</v>
+        <v>670</v>
       </c>
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27433,16 +27252,16 @@
         <v>81</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="O204" s="2"/>
       <c r="P204" t="s" s="2">
@@ -27492,7 +27311,7 @@
         <v>81</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>79</v>
@@ -27504,16 +27323,16 @@
         <v>152</v>
       </c>
       <c r="AJ204" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AK204" t="s" s="2">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="AL204" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM204" t="s" s="2">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="AN204" t="s" s="2">
         <v>81</v>
@@ -27524,10 +27343,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27550,16 +27369,16 @@
         <v>81</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
@@ -27609,7 +27428,7 @@
         <v>81</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>79</v>
@@ -27624,13 +27443,13 @@
         <v>102</v>
       </c>
       <c r="AK205" t="s" s="2">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="AL205" t="s" s="2">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="AM205" t="s" s="2">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="AN205" t="s" s="2">
         <v>81</v>
@@ -27641,10 +27460,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27756,10 +27575,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27873,10 +27692,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27899,16 +27718,16 @@
         <v>91</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
@@ -27958,7 +27777,7 @@
         <v>81</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>79</v>
@@ -27979,7 +27798,7 @@
         <v>81</v>
       </c>
       <c r="AM208" t="s" s="2">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="AN208" t="s" s="2">
         <v>81</v>
@@ -27990,10 +27809,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -28016,13 +27835,13 @@
         <v>91</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
@@ -28073,7 +27892,7 @@
         <v>81</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>79</v>
@@ -28094,7 +27913,7 @@
         <v>81</v>
       </c>
       <c r="AM209" t="s" s="2">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="AN209" t="s" s="2">
         <v>81</v>
@@ -28105,10 +27924,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28131,16 +27950,16 @@
         <v>91</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
@@ -28190,7 +28009,7 @@
         <v>81</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>90</v>
@@ -28211,7 +28030,7 @@
         <v>81</v>
       </c>
       <c r="AM210" t="s" s="2">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="AN210" t="s" s="2">
         <v>81</v>
@@ -28222,10 +28041,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -28248,16 +28067,16 @@
         <v>81</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
@@ -28307,7 +28126,7 @@
         <v>81</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>79</v>
@@ -28316,19 +28135,19 @@
         <v>80</v>
       </c>
       <c r="AI211" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ211" t="s" s="2">
-        <v>904</v>
+        <v>102</v>
       </c>
       <c r="AK211" t="s" s="2">
-        <v>905</v>
+        <v>899</v>
       </c>
       <c r="AL211" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM211" t="s" s="2">
-        <v>906</v>
+        <v>900</v>
       </c>
       <c r="AN211" t="s" s="2">
         <v>81</v>
@@ -28339,10 +28158,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>907</v>
+        <v>901</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>907</v>
+        <v>901</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28365,13 +28184,13 @@
         <v>81</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>908</v>
+        <v>902</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>909</v>
+        <v>903</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>910</v>
+        <v>904</v>
       </c>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
@@ -28422,7 +28241,7 @@
         <v>81</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>907</v>
+        <v>901</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>79</v>
@@ -28440,10 +28259,10 @@
         <v>81</v>
       </c>
       <c r="AL212" t="s" s="2">
-        <v>911</v>
+        <v>905</v>
       </c>
       <c r="AM212" t="s" s="2">
-        <v>912</v>
+        <v>906</v>
       </c>
       <c r="AN212" t="s" s="2">
         <v>81</v>
@@ -28454,10 +28273,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>913</v>
+        <v>907</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>913</v>
+        <v>907</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28569,10 +28388,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28686,14 +28505,14 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>915</v>
+        <v>909</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>915</v>
+        <v>909</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="E215" s="2"/>
       <c r="F215" t="s" s="2">
@@ -28715,16 +28534,16 @@
         <v>111</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="N215" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O215" t="s" s="2">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>81</v>
@@ -28773,7 +28592,7 @@
         <v>81</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>79</v>
@@ -28805,10 +28624,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28831,16 +28650,16 @@
         <v>81</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>908</v>
+        <v>902</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>922</v>
+        <v>916</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="O216" s="2"/>
       <c r="P216" t="s" s="2">
@@ -28890,7 +28709,7 @@
         <v>81</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>79</v>
@@ -28911,7 +28730,7 @@
         <v>81</v>
       </c>
       <c r="AM216" t="s" s="2">
-        <v>924</v>
+        <v>918</v>
       </c>
       <c r="AN216" t="s" s="2">
         <v>81</v>
@@ -28922,10 +28741,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -29037,10 +28856,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -29154,14 +28973,14 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="E219" s="2"/>
       <c r="F219" t="s" s="2">
@@ -29183,16 +29002,16 @@
         <v>111</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="N219" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O219" t="s" s="2">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="P219" t="s" s="2">
         <v>81</v>
@@ -29241,7 +29060,7 @@
         <v>81</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>79</v>
@@ -29273,10 +29092,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29299,13 +29118,13 @@
         <v>81</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="N220" t="s" s="2">
         <v>243</v>
@@ -29358,7 +29177,7 @@
         <v>81</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>79</v>
@@ -29370,7 +29189,7 @@
         <v>152</v>
       </c>
       <c r="AJ220" t="s" s="2">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="AK220" t="s" s="2">
         <v>81</v>
@@ -29379,7 +29198,7 @@
         <v>81</v>
       </c>
       <c r="AM220" t="s" s="2">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="AN220" t="s" s="2">
         <v>81</v>
@@ -29390,10 +29209,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -29416,13 +29235,13 @@
         <v>81</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="N221" t="s" s="2">
         <v>243</v>
@@ -29475,7 +29294,7 @@
         <v>81</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>79</v>
@@ -29487,7 +29306,7 @@
         <v>81</v>
       </c>
       <c r="AJ221" t="s" s="2">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="AK221" t="s" s="2">
         <v>81</v>
@@ -29496,7 +29315,7 @@
         <v>81</v>
       </c>
       <c r="AM221" t="s" s="2">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="AN221" t="s" s="2">
         <v>81</v>
@@ -29507,10 +29326,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>940</v>
+        <v>934</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>940</v>
+        <v>934</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -29533,13 +29352,13 @@
         <v>81</v>
       </c>
       <c r="K222" t="s" s="2">
+        <v>929</v>
+      </c>
+      <c r="L222" t="s" s="2">
         <v>935</v>
       </c>
-      <c r="L222" t="s" s="2">
-        <v>941</v>
-      </c>
       <c r="M222" t="s" s="2">
-        <v>942</v>
+        <v>936</v>
       </c>
       <c r="N222" t="s" s="2">
         <v>243</v>
@@ -29592,7 +29411,7 @@
         <v>81</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>940</v>
+        <v>934</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>79</v>
@@ -29604,7 +29423,7 @@
         <v>81</v>
       </c>
       <c r="AJ222" t="s" s="2">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="AK222" t="s" s="2">
         <v>81</v>
@@ -29613,7 +29432,7 @@
         <v>81</v>
       </c>
       <c r="AM222" t="s" s="2">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="AN222" t="s" s="2">
         <v>81</v>
@@ -29624,10 +29443,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29650,19 +29469,19 @@
         <v>81</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>944</v>
+        <v>938</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="N223" t="s" s="2">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="O223" t="s" s="2">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="P223" t="s" s="2">
         <v>81</v>
@@ -29711,7 +29530,7 @@
         <v>81</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>79</v>
@@ -29723,30 +29542,30 @@
         <v>152</v>
       </c>
       <c r="AJ223" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AK223" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL223" t="s" s="2">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="AM223" t="s" s="2">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="AN223" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO223" t="s" s="2">
-        <v>950</v>
+        <v>944</v>
       </c>
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29769,16 +29588,16 @@
         <v>81</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>952</v>
+        <v>946</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>954</v>
+        <v>948</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>955</v>
+        <v>949</v>
       </c>
       <c r="O224" s="2"/>
       <c r="P224" t="s" s="2">
@@ -29828,7 +29647,7 @@
         <v>81</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>79</v>
@@ -29846,24 +29665,24 @@
         <v>81</v>
       </c>
       <c r="AL224" t="s" s="2">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="AM224" t="s" s="2">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="AN224" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO224" t="s" s="2">
-        <v>958</v>
+        <v>952</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -29886,13 +29705,13 @@
         <v>81</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="N225" t="s" s="2">
         <v>243</v>
@@ -29945,7 +29764,7 @@
         <v>81</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>79</v>
@@ -29957,30 +29776,30 @@
         <v>152</v>
       </c>
       <c r="AJ225" t="s" s="2">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="AK225" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL225" t="s" s="2">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="AM225" t="s" s="2">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="AN225" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO225" t="s" s="2">
-        <v>964</v>
+        <v>958</v>
       </c>
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -30092,10 +29911,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>966</v>
+        <v>960</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>966</v>
+        <v>960</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -30209,10 +30028,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -30238,10 +30057,10 @@
         <v>254</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="N228" t="s" s="2">
         <v>257</v>
@@ -30328,10 +30147,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -30360,7 +30179,7 @@
         <v>264</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" t="s" s="2">
@@ -30447,10 +30266,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -30564,10 +30383,10 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30610,7 +30429,7 @@
         <v>81</v>
       </c>
       <c r="S231" t="s" s="2">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="T231" t="s" s="2">
         <v>81</v>
@@ -30681,10 +30500,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -30800,10 +30619,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -30826,16 +30645,16 @@
         <v>81</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="N233" t="s" s="2">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="O233" s="2"/>
       <c r="P233" t="s" s="2">
@@ -30885,7 +30704,7 @@
         <v>81</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>79</v>
@@ -30897,16 +30716,16 @@
         <v>81</v>
       </c>
       <c r="AJ233" t="s" s="2">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="AK233" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL233" t="s" s="2">
-        <v>979</v>
+        <v>973</v>
       </c>
       <c r="AM233" t="s" s="2">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="AN233" t="s" s="2">
         <v>81</v>
@@ -30917,10 +30736,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -30943,16 +30762,16 @@
         <v>81</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>478</v>
+        <v>412</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="N234" t="s" s="2">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="O234" s="2"/>
       <c r="P234" t="s" s="2">
@@ -31002,7 +30821,7 @@
         <v>81</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>79</v>
@@ -31014,7 +30833,7 @@
         <v>152</v>
       </c>
       <c r="AJ234" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AK234" t="s" s="2">
         <v>81</v>
@@ -31023,10 +30842,10 @@
         <v>81</v>
       </c>
       <c r="AM234" t="s" s="2">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="AN234" t="s" s="2">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="AO234" t="s" s="2">
         <v>81</v>
@@ -31034,10 +30853,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -31060,13 +30879,13 @@
         <v>81</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>908</v>
+        <v>902</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="N235" s="2"/>
       <c r="O235" s="2"/>
@@ -31117,7 +30936,7 @@
         <v>81</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>79</v>
@@ -31135,10 +30954,10 @@
         <v>81</v>
       </c>
       <c r="AL235" t="s" s="2">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="AM235" t="s" s="2">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="AN235" t="s" s="2">
         <v>81</v>
@@ -31149,10 +30968,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -31264,10 +31083,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -31381,14 +31200,14 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="E238" s="2"/>
       <c r="F238" t="s" s="2">
@@ -31410,16 +31229,16 @@
         <v>111</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="N238" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O238" t="s" s="2">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="P238" t="s" s="2">
         <v>81</v>
@@ -31468,7 +31287,7 @@
         <v>81</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>79</v>
@@ -31500,10 +31319,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -31529,13 +31348,13 @@
         <v>221</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="N239" t="s" s="2">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="O239" s="2"/>
       <c r="P239" t="s" s="2">
@@ -31585,7 +31404,7 @@
         <v>81</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>90</v>
@@ -31603,24 +31422,24 @@
         <v>81</v>
       </c>
       <c r="AL239" t="s" s="2">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="AM239" t="s" s="2">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="AN239" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO239" t="s" s="2">
-        <v>998</v>
+        <v>992</v>
       </c>
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -31643,16 +31462,16 @@
         <v>81</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="N240" t="s" s="2">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="O240" s="2"/>
       <c r="P240" t="s" s="2">
@@ -31681,10 +31500,10 @@
         <v>159</v>
       </c>
       <c r="Y240" t="s" s="2">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="Z240" t="s" s="2">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="AA240" t="s" s="2">
         <v>81</v>
@@ -31702,7 +31521,7 @@
         <v>81</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>79</v>
@@ -31720,24 +31539,24 @@
         <v>81</v>
       </c>
       <c r="AL240" t="s" s="2">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="AM240" t="s" s="2">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="AN240" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO240" t="s" s="2">
-        <v>1007</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -31760,16 +31579,16 @@
         <v>81</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="N241" t="s" s="2">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="O241" s="2"/>
       <c r="P241" t="s" s="2">
@@ -31819,7 +31638,7 @@
         <v>81</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>79</v>
@@ -31831,16 +31650,16 @@
         <v>152</v>
       </c>
       <c r="AJ241" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AK241" t="s" s="2">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="AL241" t="s" s="2">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="AM241" t="s" s="2">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="AN241" t="s" s="2">
         <v>81</v>
@@ -31851,14 +31670,14 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="E242" s="2"/>
       <c r="F242" t="s" s="2">
@@ -31877,16 +31696,16 @@
         <v>81</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="N242" t="s" s="2">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="O242" s="2"/>
       <c r="P242" t="s" s="2">
@@ -31936,7 +31755,7 @@
         <v>81</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>79</v>
@@ -31948,7 +31767,7 @@
         <v>152</v>
       </c>
       <c r="AJ242" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AK242" t="s" s="2">
         <v>81</v>
@@ -31957,7 +31776,7 @@
         <v>81</v>
       </c>
       <c r="AM242" t="s" s="2">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="AN242" t="s" s="2">
         <v>81</v>
@@ -31968,10 +31787,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -31994,16 +31813,16 @@
         <v>81</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>1024</v>
+        <v>1018</v>
       </c>
       <c r="N243" t="s" s="2">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="O243" s="2"/>
       <c r="P243" t="s" s="2">
@@ -32053,7 +31872,7 @@
         <v>81</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>79</v>
@@ -32065,16 +31884,16 @@
         <v>152</v>
       </c>
       <c r="AJ243" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AK243" t="s" s="2">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="AL243" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM243" t="s" s="2">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="AN243" t="s" s="2">
         <v>81</v>
